--- a/public/data/summer-prep-optimization/industry-optimization-inputs.xlsx
+++ b/public/data/summer-prep-optimization/industry-optimization-inputs.xlsx
@@ -576,9 +576,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -593,9 +591,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -610,9 +606,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -627,9 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -644,9 +636,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -670,9 +660,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -4523,7 +4511,7 @@
         <v>2025</v>
       </c>
       <c r="I2" s="15" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="J2" s="15" t="n">
         <v>0</v>
@@ -4569,7 +4557,7 @@
         <v>2030</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.6</v>
@@ -4615,7 +4603,7 @@
         <v>2025</v>
       </c>
       <c r="I4" s="15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J4" s="15" t="n">
         <v>0</v>
@@ -4661,7 +4649,7 @@
         <v>2027</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>0</v>
@@ -4707,7 +4695,7 @@
         <v>2025</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="J6" s="15" t="n">
         <v>0</v>
@@ -4753,7 +4741,7 @@
         <v>2025</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>0</v>
@@ -4845,7 +4833,7 @@
         <v>2028</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>0.9</v>
@@ -4891,7 +4879,7 @@
         <v>2025</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>0</v>
@@ -4937,7 +4925,7 @@
         <v>2025</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>0</v>
@@ -4983,7 +4971,7 @@
         <v>2030</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="J12" s="15" t="n">
         <v>0</v>
@@ -5029,7 +5017,7 @@
         <v>2027</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0</v>
@@ -5075,7 +5063,7 @@
         <v>2032</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="J14" s="15" t="n">
         <v>0.65</v>
@@ -5121,7 +5109,7 @@
         <v>2025</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0</v>
@@ -5167,7 +5155,7 @@
         <v>2026</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J16" s="15" t="n">
         <v>0.6</v>
@@ -5213,7 +5201,7 @@
         <v>2026</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>0</v>
@@ -5259,7 +5247,7 @@
         <v>2025</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="J18" s="15" t="n">
         <v>0</v>
@@ -5305,7 +5293,7 @@
         <v>2032</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>0</v>
@@ -5351,7 +5339,7 @@
         <v>2025</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>0</v>
@@ -5397,7 +5385,7 @@
         <v>2025</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0</v>
@@ -5443,7 +5431,7 @@
         <v>2025</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="J22" s="15" t="n">
         <v>0</v>
@@ -5489,7 +5477,7 @@
         <v>2027</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="J23" s="18" t="n">
         <v>0</v>
@@ -5535,7 +5523,7 @@
         <v>2025</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="J24" s="15" t="n">
         <v>0</v>
@@ -5581,7 +5569,7 @@
         <v>2027</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>0</v>
@@ -5627,7 +5615,7 @@
         <v>2025</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="J26" s="15" t="n">
         <v>0</v>

--- a/public/data/summer-prep-optimization/industry-optimization-inputs.xlsx
+++ b/public/data/summer-prep-optimization/industry-optimization-inputs.xlsx
@@ -20,16 +20,16 @@
     <sheet name="Sources" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sectors'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Demand'!$A$1:$C$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Technologies'!$A$1:$L$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Energy Use'!$A$1:$C$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fuel Prices'!$A$1:$C$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Carbon Price'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Emission Factors'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Scenarios'!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Sources'!$A$1:$G$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sectors'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Demand'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Technologies'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Energy Use'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fuel Prices'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Carbon Price'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Emission Factors'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$F$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Scenarios'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Sources'!$A$1:$G$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +41,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +81,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10.5"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -135,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +165,9 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -167,6 +176,9 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -563,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -576,7 +588,9 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -591,7 +605,9 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -606,7 +622,9 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -621,7 +639,9 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -636,7 +656,9 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -660,16 +682,35 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>Per-row sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="110" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Every data sheet (all except 'sources') carries 'source' and 'source_url' as its last two columns: 'source' is a short citation (Org (Year), Title) and 'source_url' is one working link, wherever possible deep-linking to the exact report or dataset page the number came from (clickable in this sheet). Rows that are genuine modelling choices rather than literature values say so honestly: 'Derived from &lt;source&gt;' for demand paths and the carbon price low/high bands built around a sourced central path, and 'Model assumption (prototype)' for the 13 sensitivity-scenario multipliers in the 'scenarios' sheet, whose source_url points to this model's own README rather than an invented external reference. The 'sources' sheet remains the master register of every citation used, including secondary/cross-check sources not selected as a given row's primary link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>Model &amp; downloads</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>The optimization model itself (Julia + JuMP/HiGHS) lives in the ESABCCMethodHub repo under beta/modules/summer-prep/optimization/model/, in the spirit of the SEAMAPS model (https://github.com/SebastianFra/SEAMAPS). This workbook, the Julia source and the full model bundle (code + data + results + README) are available for download from the 'Summer Prep — Industry Optimization' page of the ESABCC Method Hub.</t>
         </is>
@@ -686,13 +727,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -716,6 +759,16 @@
           <t>factor</t>
         </is>
       </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -733,28 +786,48 @@
           <t>none</t>
         </is>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>co2_low</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>EU ETS carbon price follows the low column of carbon_price.csv</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>carbon_price_low</t>
         </is>
       </c>
-      <c r="D3" s="21" t="n">
+      <c r="D3" s="23" t="n">
         <v>1</v>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -773,28 +846,48 @@
           <t>carbon_price_high</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>capex_low</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Clean (non-reference) technology CAPEX 30% lower (faster learning/cost-down)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>capex_clean</t>
         </is>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="23" t="n">
         <v>0.7</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -813,28 +906,48 @@
           <t>capex_clean</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="22" t="n">
         <v>1.3</v>
       </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>demand_low</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Product demand 20% lower across all subsectors (material efficiency &amp; circularity)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>demand</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="23" t="n">
         <v>0.8</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -853,28 +966,48 @@
           <t>demand</t>
         </is>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="22" t="n">
         <v>1.1</v>
       </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>elec_cheap</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Electricity price 30% lower (faster renewables build-out)</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>elec_price</t>
         </is>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="23" t="n">
         <v>0.7</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -893,28 +1026,48 @@
           <t>elec_price</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="22" t="n">
         <v>1.3</v>
       </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>h2_cheap</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Hydrogen price 40% lower (electrolyser cost-down, cheap renewable power)</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>h2_price</t>
         </is>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="23" t="n">
         <v>0.6</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -933,28 +1086,48 @@
           <t>h2_price</t>
         </is>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="22" t="n">
         <v>1.4</v>
       </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>eff_gain</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Energy intensity of clean technologies 10% lower (learning-by-doing efficiency gains)</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>energy_intensity_clean</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="23" t="n">
         <v>0.9</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -973,12 +1146,22 @@
           <t>max_build_share</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="22" t="n">
         <v>0.5</v>
       </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D14"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -989,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1059,9 +1242,9 @@
           <t>European Steel in Figures 2024</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.eurofer.eu/publications/economic-market-outlook/european-steel-in-figures-2024</t>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -1076,37 +1259,37 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Sandbag (EEA EU ETS Data Viewer / EUTL)</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>A closer look at 2023 emissions</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>https://sandbag.be/2024/10/07/a-closer-look-at-2023-emissions/</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>EU ETS 'pig iron or steel' activity ~96 Mt CO2 (2023); ~145 Mt on a value-chain basis incl. coke ovens</t>
         </is>
@@ -1133,9 +1316,9 @@
           <t>Key Facts &amp; Figures</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>https://cembureau.eu/about-our-industry/key-facts-figures/</t>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1150,37 +1333,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>cement</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Sandbag (EEA EU ETS Data Viewer / EUTL)</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>A closer look at 2023 emissions</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>https://sandbag.be/2024/10/07/a-closer-look-at-2023-emissions/</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>EU ETS 'cement clinker or lime' activity combined ~124 Mt CO2 (2023)</t>
         </is>
@@ -1207,7 +1390,7 @@
           <t>Chemicals in the CBAM: Time to step up</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>https://sandbag.be/2025/11/25/chemicals-in-the-cbam-time-to-step-up/</t>
         </is>
@@ -1224,37 +1407,37 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>hvc</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>The Future of Petrochemicals</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>EU-27 HVC (ethylene/propylene/BTX) production order of magnitude ~40 Mt/yr</t>
         </is>
@@ -1281,9 +1464,9 @@
           <t>Industry Facts &amp; Figures</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fertilizerseurope.com/industry-facts-figures/</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1298,37 +1481,37 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>ammonia</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Ammonia Technology Roadmap</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Direct CO2 intensity of conventional (SMR) ammonia ~1.6-2.4 tCO2/t NH3; EU-27 direct CO2 estimated ~26 Mt/yr</t>
         </is>
@@ -1355,7 +1538,7 @@
           <t>Primary Aluminium Production statistics</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>https://international-aluminium.org/statistics/</t>
         </is>
@@ -1372,37 +1555,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>JRC (European Commission)</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Aluminium factsheet (JRC144120)</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Direct process CO2 (anode consumption) ~2.75 Mt CO2 (2022)</t>
         </is>
@@ -1429,7 +1612,7 @@
           <t>Statistics</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>https://feve.org/about-glass/statistics/</t>
         </is>
@@ -1446,37 +1629,37 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>glass</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>European Commission (CINEA)</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>How LIFE is reducing emissions from glass production</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Whole glass sector ~22 Mt CO2 direct/yr; container+flat share estimated ~20 Mt</t>
         </is>
@@ -1503,7 +1686,7 @@
           <t>Key Statistics 2022 - European pulp &amp; paper industry</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
         </is>
@@ -1520,37 +1703,37 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>steel_bfbof</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Iron and Steel Technology Roadmap</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Reference BF-BOF energy/capex/direct-CO2 order of magnitude (~1.9 tCO2/t)</t>
         </is>
@@ -1577,7 +1760,7 @@
           <t>Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
         </is>
@@ -1594,37 +1777,37 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>steel_ngdri_eaf</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Iron and Steel Technology Roadmap</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>NG-DRI+EAF energy use and transitional-asset characterisation</t>
         </is>
@@ -1651,7 +1834,7 @@
           <t>Carbon-free steel production - Cost reduction options and usage of existing gas infrastructure</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>https://www.europarl.europa.eu/RegData/etudes/STUD/2021/690008/EPRS_STU(2021)690008_EN.pdf</t>
         </is>
@@ -1668,37 +1851,37 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>steel_h2dri_eaf</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>LeadIT (SEI)</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Green Steel Tracker</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>https://www.industrytransition.org/green-steel-tracker/</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>Commercial availability timeline (first plants building now)</t>
         </is>
@@ -1725,7 +1908,7 @@
           <t>Iron and Steel Technology Roadmap</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
         </is>
@@ -1742,37 +1925,37 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>steel_scrap_eaf</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Material Economics</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/node/13</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Scrap availability as the binding long-run constraint on secondary steel</t>
         </is>
@@ -1799,7 +1982,7 @@
           <t>Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
         </is>
@@ -1816,37 +1999,37 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>cement_clinkersub</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>MDPI (Sustainability, peer-reviewed)</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Limestone Calcined Clay Cement (LC3): From Laboratory Innovation to Sustainable Industrial Application</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>https://www.mdpi.com/2071-1050/18/7/3473</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>LC3 clinker replacement up to ~50%, ~40% CO2 cut, near-cost-neutral</t>
         </is>
@@ -1873,7 +2056,7 @@
           <t>Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
         </is>
@@ -1890,37 +2073,37 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>cement_ccs</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Heidelberg Materials</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>World premiere: CCS cement facility opens in Norway (Brevik CCS)</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>https://www.heidelbergmaterials.com/en/pr-2025-06-18</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>First industrial-scale cement CCS operational since 2025; available_from calibrated to this</t>
         </is>
@@ -1947,7 +2130,7 @@
           <t>Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
         </is>
@@ -1964,37 +2147,37 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>hvc_ref</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>The Future of Petrochemicals</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>Reference steam-cracker furnace energy intensity order of magnitude</t>
         </is>
@@ -2021,7 +2204,7 @@
           <t>Start-up of the world's first large-scale electrically heated steam cracking furnace</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>https://www.basf.com/global/en/media/news-releases/2024/04/p-24-177</t>
         </is>
@@ -2038,37 +2221,37 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>hvc_bio</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>The Future of Petrochemicals</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Bio-naphtha as drop-in feedstock displacing fossil naphtha</t>
         </is>
@@ -2095,7 +2278,7 @@
           <t>Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
         </is>
@@ -2112,37 +2295,37 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>ammonia_smr</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Ammonia Technology Roadmap</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Reference SMR-Haber-Bosch natural gas intensity ~28-32 GJ/t NH3</t>
         </is>
@@ -2169,7 +2352,7 @@
           <t>Ammonia Technology Roadmap</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
         </is>
@@ -2186,37 +2369,37 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>ammonia_h2</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Ammonia Technology Roadmap - Executive Summary</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/ammonia-technology-roadmap/executive-summary</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Electrolytic-H2 ammonia MAC ~US$820/t NH3 (~US$400/t above conventional); needs power &lt;~US$40/MWh for parity</t>
         </is>
@@ -2243,7 +2426,7 @@
           <t>Yara opens renewable hydrogen plant: a major milestone</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>https://www.yara.com/corporate-releases/yara-opens-renewable-hydrogen-plant-a-major-milestone/</t>
         </is>
@@ -2260,37 +2443,37 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>alu_ref</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>JRC (European Commission)</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Aluminium factsheet (JRC144120)</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>Direct anode process CO2 ~1.4 tCO2/t primary Al implied by ~2.75 Mt / ~2 Mt production</t>
         </is>
@@ -2317,7 +2500,7 @@
           <t>Statistics</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>https://international-aluminium.org/statistics/</t>
         </is>
@@ -2334,37 +2517,37 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>alu_inert</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>ELYSIS</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>ELYSIS achieves breakthrough with commercial-size cell</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>https://elysis.com/en/elysis-achieves-breakthrough-with-commercial-size-cell-a-first-in-aluminium-production-using-the</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>Full-scale 450 kA commercial-size inert-anode cell started up Nov 2025; eliminates direct process CO2</t>
         </is>
@@ -2391,9 +2574,9 @@
           <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/node/13</t>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -2408,37 +2591,37 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>glass_ng</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>European Commission (CINEA)</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>How LIFE is reducing emissions from glass production</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>Reference gas-fired melting energy ~5-7 GJ/t and process CO2 from carbonate raw materials</t>
         </is>
@@ -2465,7 +2648,7 @@
           <t>ETP Clean Energy Technology Guide (technology readiness levels)</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
         </is>
@@ -2482,37 +2665,37 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>glass_hybrid</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>ETP Clean Energy Technology Guide (technology readiness levels)</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>Large hybrid furnace TRL 6-8, emerging</t>
         </is>
@@ -2539,7 +2722,7 @@
           <t>Key Statistics 2022 - European pulp &amp; paper industry</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
         </is>
@@ -2556,37 +2739,37 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>paper_elec</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>The Future of Heat Pumps</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/the-future-of-heat-pumps</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>Industrial heat-pump electrification of process heat; TRL and availability</t>
         </is>
@@ -2613,7 +2796,7 @@
           <t>Decarbonizing industrial process heat: the role of biomass</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
         </is>
@@ -2630,37 +2813,37 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>fuel_prices</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>coal</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>World Energy Outlook 2024</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>Steam coal industrial price path, central scenario order of magnitude ~EUR3/GJ</t>
         </is>
@@ -2687,7 +2870,7 @@
           <t>World Energy Outlook 2024</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
         </is>
@@ -2704,37 +2887,37 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>fuel_prices</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>World Energy Outlook 2024</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>EU industrial natural gas price path, central scenario, declining from ~EUR10/GJ (2025)</t>
         </is>
@@ -2761,7 +2944,7 @@
           <t>Electricity price statistics</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
         </is>
@@ -2778,37 +2961,37 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>fuel_prices</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Global Hydrogen Review 2024</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Low-carbon hydrogen cost path ~EUR40/GJ (~EUR4.8/kg) in 2025 falling to ~EUR20/GJ (~EUR2.4/kg) by 2050</t>
         </is>
@@ -2835,7 +3018,7 @@
           <t>Decarbonizing industrial process heat: the role of biomass</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
         </is>
@@ -2852,37 +3035,37 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>fuel_prices</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>IEA</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>World Energy Outlook 2024</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Industrial oil/naphtha price path, central scenario order of magnitude ~EUR14/GJ</t>
         </is>
@@ -2909,9 +3092,9 @@
           <t>2040 Climate Target</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>https://climate.ec.europa.eu/eu-action/eu-climate-targets-and-progress/2040-climate-target_en</t>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2926,37 +3109,37 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>carbon_price</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>eu_ets</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>ICAP</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>EU Emissions Trading System (EU ETS)</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>https://icapcarbonaction.com/en/ets/eu-emissions-trading-system-eu-ets</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>Historical and current EUA price context used to anchor the 2025 starting point</t>
         </is>
@@ -2983,7 +3166,7 @@
           <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
         </is>
@@ -3000,37 +3183,37 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>emission_factors</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>coke</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>IPCC</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>Default combustion emission factor for coke oven coke, ~107 kgCO2/GJ</t>
         </is>
@@ -3057,7 +3240,7 @@
           <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
         </is>
@@ -3074,37 +3257,37 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>emission_factors</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>IPCC</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="G57" s="10" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>Default combustion emission factor for gas/diesel oil &amp; naphtha, ~73 kgCO2/GJ</t>
         </is>
@@ -3131,7 +3314,7 @@
           <t>Chapter 11: Industry</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
         </is>
@@ -3148,37 +3331,37 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>emission_factors</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>biomass</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>IPCC AR6 WGIII</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>Chapter 11: Industry</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="G59" s="11" t="inlineStr">
         <is>
           <t>Biomass combustion CO2 conventionally reported as zero at point of combustion (biogenic carbon accounting); land-use/supply-chain emissions not modelled here</t>
         </is>
@@ -3205,7 +3388,7 @@
           <t>Greenhouse gas emission intensity of electricity generation (indicator)</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
         </is>
@@ -3222,37 +3405,37 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>constraints</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>scrap_share_max</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>Material Economics</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/node/13</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>Steel scrap availability rising from ~45% (2025) to ~55% (2050) of demand servable by scrap-EAF; aluminium secondary share rising ~55% to ~65%, both circularity-constrained</t>
         </is>
@@ -3279,7 +3462,7 @@
           <t>Brief on biomass for energy in the European Union</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
         </is>
@@ -3296,37 +3479,37 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>constraints</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>ccs_mt_max</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>Global CCS Institute</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>Global Status of CCS report series</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>https://www.globalccsinstitute.com/</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>EU CO2 transport &amp; storage network ramp-up: ~0 Mt/yr (2025) to ~100 Mt/yr (2050) capturable across all subsectors</t>
         </is>
@@ -3353,7 +3536,7 @@
           <t>Carbon capture and storage in Europe: slow but significant progress in 2025</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>https://www.catf.us/2025/11/carbon-capture-storage-europe-slow-but-significant-progress-2025/</t>
         </is>
@@ -3370,37 +3553,37 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>demand</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>Eurofer</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>European Steel in Figures 2024</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>https://www.eurofer.eu/publications/economic-market-outlook/european-steel-in-figures-2024</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>Demand path assumed broadly flat-to-declining from the 2023 production base</t>
         </is>
@@ -3427,9 +3610,9 @@
           <t>Key Facts &amp; Figures</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>https://cembureau.eu/about-our-industry/key-facts-figures/</t>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -3444,37 +3627,37 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>demand</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>International Aluminium Institute (IAI)</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>Statistics</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>https://international-aluminium.org/statistics/</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>Demand path assumed slight growth, reflecting continued electrification-driven aluminium demand</t>
         </is>
@@ -3501,7 +3684,7 @@
           <t>The Future of Petrochemicals</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
         </is>
@@ -3518,44 +3701,265 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>discount_rate</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>IPCC</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>AR6 WGIII, Chapter 11: Industry</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr">
         <is>
           <t>7% social/industry discount rate and capital recovery factor approach used to annualise CAPEX, consistent with standard industrial decarbonisation cost-modelling practice</t>
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>ammonia</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Fertilizers Europe</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Fertilizer Industry Facts and Figures 2023 edition</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Demand path assumed broadly flat-to-slightly-declining from the 2023 production base</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>FEVE (European Container Glass Federation)</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Statistics</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>https://feve.org/about-glass/statistics/</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Demand path assumed broadly flat from the 2023 production base</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>CEPI</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Demand path assumed gently declining from the 2023 production base</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>scenarios</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>ESABCC Method Hub (model team)</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Model README - sensitivity scenario methodology</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>All 13 scenarios (1 central + 12 sensitivities) are prototype modelling assumptions (parameter multipliers applied to already-sourced central inputs), not independent literature values; see the README for the full methodology and per-scenario definitions.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G69"/>
+  <autoFilter ref="A1:G73"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3566,7 +3970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3574,7 +3978,8 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3608,6 +4013,11 @@
           <t>source</t>
         </is>
       </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -3633,35 +4043,45 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Eurofer 2024 / Sandbag EUTL 2023</t>
+          <t>Eurofer (2024), European Steel in Figures 2024; Sandbag (EEA EU ETS Data Viewer / EUTL) (2024), A closer look at 2023 emissions</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>cement</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Cement (clinker-based)</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Non-metallic minerals</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Cembureau 2024 / Sandbag EUTL 2023</t>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Cembureau (2024), Key Facts &amp; Figures; Sandbag (EEA EU ETS Data Viewer / EUTL) (2024), A closer look at 2023 emissions</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
         </is>
       </c>
     </row>
@@ -3689,35 +4109,45 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Sandbag Chemicals 2025 / IEA Future of Petrochemicals</t>
+          <t>Sandbag (EU ETS / EUTL) (2025), Chemicals in the CBAM: Time to step up; IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>https://sandbag.be/2025/11/25/chemicals-in-the-cbam-time-to-step-up/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>ammonia</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Ammonia / nitrogen fertilisers</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Chemicals &amp; refining</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>Fertilizers Europe 2024 / IEA Ammonia Technology Roadmap 2021</t>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Fertilizers Europe (2024), Industry Facts &amp; Figures; IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
         </is>
       </c>
     </row>
@@ -3745,35 +4175,45 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>IAI 2024 / JRC Aluminium factsheet 2026</t>
+          <t>International Aluminium Institute (IAI) (2024), Primary Aluminium Production statistics; JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>https://international-aluminium.org/statistics/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>glass</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Container &amp; flat glass</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Non-metallic minerals</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>FEVE / European Commission (CINEA) 2022</t>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>FEVE (European Container Glass Federation) (2024), Statistics; European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>https://feve.org/about-glass/statistics/</t>
         </is>
       </c>
     </row>
@@ -3801,12 +4241,26 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>CEPI Key Statistics 2022</t>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:G8"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3817,12 +4271,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3841,6 +4297,16 @@
           <t>demand_mt</t>
         </is>
       </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -3848,24 +4314,44 @@
           <t>steel</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C2" s="8" t="n">
         <v>124</v>
       </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Eurofer (2024), European Steel in Figures 2024 (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="12" t="n">
         <v>122</v>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Eurofer (2024), European Steel in Figures 2024 (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3874,24 +4360,44 @@
           <t>steel</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>120</v>
       </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Eurofer (2024), European Steel in Figures 2024 (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>118</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Eurofer (2024), European Steel in Figures 2024 (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3900,24 +4406,44 @@
           <t>steel</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>116</v>
       </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Eurofer (2024), European Steel in Figures 2024 (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>114</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Eurofer (2024), European Steel in Figures 2024 (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3926,24 +4452,44 @@
           <t>cement</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>178</v>
       </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Cembureau (2024), Key Facts &amp; Figures (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>cement</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>175</v>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Cembureau (2024), Key Facts &amp; Figures (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -3952,24 +4498,44 @@
           <t>cement</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>172</v>
       </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Cembureau (2024), Key Facts &amp; Figures (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>cement</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>168</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Cembureau (2024), Key Facts &amp; Figures (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -3978,24 +4544,44 @@
           <t>cement</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>164</v>
       </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Cembureau (2024), Key Facts &amp; Figures (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>cement</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>160</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Cembureau (2024), Key Facts &amp; Figures (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4004,24 +4590,44 @@
           <t>hvc</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Derived from IEA (2018), The Future of Petrochemicals (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>hvc</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>41</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Derived from IEA (2018), The Future of Petrochemicals (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -4030,24 +4636,44 @@
           <t>hvc</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>42</v>
       </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Derived from IEA (2018), The Future of Petrochemicals (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>hvc</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>43</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Derived from IEA (2018), The Future of Petrochemicals (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -4056,24 +4682,44 @@
           <t>hvc</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Derived from IEA (2018), The Future of Petrochemicals (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>hvc</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <v>45</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Derived from IEA (2018), The Future of Petrochemicals (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -4082,24 +4728,44 @@
           <t>ammonia</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>16</v>
       </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Fertilizers Europe (2024), Fertilizer Industry Facts and Figures 2023 edition (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>ammonia</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B21" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <v>16</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Fertilizers Europe (2024), Fertilizer Industry Facts and Figures 2023 edition (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -4108,24 +4774,44 @@
           <t>ammonia</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Fertilizers Europe (2024), Fertilizer Industry Facts and Figures 2023 edition (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>ammonia</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="12" t="n">
         <v>15</v>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Fertilizers Europe (2024), Fertilizer Industry Facts and Figures 2023 edition (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -4134,24 +4820,44 @@
           <t>ammonia</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>14</v>
       </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Derived from Fertilizers Europe (2024), Fertilizer Industry Facts and Figures 2023 edition (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>ammonia</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="12" t="n">
         <v>14</v>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Derived from Fertilizers Europe (2024), Fertilizer Industry Facts and Figures 2023 edition (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -4160,24 +4866,44 @@
           <t>aluminium</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>6.5</v>
       </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Derived from International Aluminium Institute (IAI) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>https://international-aluminium.org/statistics/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="12" t="n">
         <v>6.8</v>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Derived from International Aluminium Institute (IAI) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>https://international-aluminium.org/statistics/</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -4186,24 +4912,44 @@
           <t>aluminium</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>7.1</v>
       </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Derived from International Aluminium Institute (IAI) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>https://international-aluminium.org/statistics/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B29" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" s="12" t="n">
         <v>7.4</v>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Derived from International Aluminium Institute (IAI) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>https://international-aluminium.org/statistics/</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -4212,24 +4958,44 @@
           <t>aluminium</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>7.7</v>
       </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Derived from International Aluminium Institute (IAI) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>https://international-aluminium.org/statistics/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="12" t="n">
         <v>8</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Derived from International Aluminium Institute (IAI) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>https://international-aluminium.org/statistics/</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -4238,24 +5004,44 @@
           <t>glass</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>35</v>
       </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Derived from FEVE (European Container Glass Federation) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>https://feve.org/about-glass/statistics/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>glass</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C33" s="12" t="n">
         <v>35</v>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Derived from FEVE (European Container Glass Federation) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>https://feve.org/about-glass/statistics/</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -4264,24 +5050,44 @@
           <t>glass</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>34</v>
       </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Derived from FEVE (European Container Glass Federation) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>https://feve.org/about-glass/statistics/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>glass</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="C35" s="12" t="n">
         <v>34</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Derived from FEVE (European Container Glass Federation) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>https://feve.org/about-glass/statistics/</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -4290,24 +5096,44 @@
           <t>glass</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Derived from FEVE (European Container Glass Federation) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>https://feve.org/about-glass/statistics/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>glass</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n">
+      <c r="B37" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="C37" s="12" t="n">
         <v>33</v>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Derived from FEVE (European Container Glass Federation) (2024), Statistics (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>https://feve.org/about-glass/statistics/</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -4316,24 +5142,44 @@
           <t>paper</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>74</v>
       </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Derived from CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>paper</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n">
+      <c r="B39" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="C39" s="12" t="n">
         <v>72</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Derived from CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -4342,24 +5188,44 @@
           <t>paper</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>70</v>
       </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Derived from CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>paper</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
+      <c r="B41" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C41" s="11" t="n">
+      <c r="C41" s="12" t="n">
         <v>68</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Derived from CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -4368,28 +5234,92 @@
           <t>paper</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>66</v>
       </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Derived from CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>paper</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C43" s="11" t="n">
+      <c r="C43" s="12" t="n">
         <v>64</v>
       </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Derived from CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry (2023 production baseline)</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C43"/>
+  <autoFilter ref="A1:E43"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4400,7 +5330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4414,7 +5344,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4478,6 +5409,11 @@
           <t>source</t>
         </is>
       </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -4495,79 +5431,89 @@
           <t>Blast furnace - basic oxygen furnace (reference)</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="16" t="n">
         <v>400</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I2" s="15" t="n">
+      <c r="I2" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="J2" s="15" t="n">
+      <c r="J2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="16" t="n">
+      <c r="K2" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>IEA Iron and Steel Technology Roadmap 2020</t>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>steel_bfbof_ccs</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>BF-BOF with CCUS (top-gas / post-combustion capture)</t>
         </is>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="19" t="n">
         <v>650</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="19" t="n">
         <v>160</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="20" t="n">
         <v>0.12</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>IEAGHG 2018 / IEA Iron and Steel Technology Roadmap 2020</t>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
         </is>
       </c>
     </row>
@@ -4587,79 +5533,89 @@
           <t>Natural-gas DRI + EAF (transitional)</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="16" t="n">
         <v>140</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J4" s="15" t="n">
+      <c r="J4" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K4" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>IEA Iron and Steel Technology Roadmap 2020</t>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>steel_h2dri_eaf</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Hydrogen DRI (H2-DRI) + EAF</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="19" t="n">
         <v>800</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="19" t="n">
         <v>130</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="15" t="n">
         <v>2027</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="20" t="n">
         <v>0.15</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>EPRS 2021 (Carbon-free steel production) / LeadIT Green Steel Tracker</t>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>European Parliament (EPRS) (2021), Carbon-free steel production - Cost reduction options and usage of existing gas infrastructure; LeadIT (SEI) (2026), Green Steel Tracker</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/RegData/etudes/STUD/2021/690008/EPRS_STU(2021)690008_EN.pdf</t>
         </is>
       </c>
     </row>
@@ -4679,79 +5635,89 @@
           <t>Scrap-based EAF (secondary steel, scrap-limited)</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="16" t="n">
         <v>280</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="16" t="n">
+      <c r="K6" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>IEA Iron and Steel Technology Roadmap 2020 / Material Economics 2019</t>
+          <t>IEA (2020), Iron and Steel Technology Roadmap; Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>cement_ref</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>cement</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Conventional dry-kiln clinker production (reference)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="19" t="n">
         <v>150</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="21" t="n">
         <v>0.408</v>
       </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>IEA/CSI Cement Technology Roadmap 2018</t>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
         </is>
       </c>
     </row>
@@ -4771,79 +5737,89 @@
           <t>Clinker substitution / calcined clay (LC3) &amp; efficiency package</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="16" t="n">
         <v>160</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="18" t="n">
         <v>0.345</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>MDPI Sustainability (LC3) 2026 / Material Economics 2019</t>
+          <t>MDPI (Sustainability, peer-reviewed) (2026), Limestone Calcined Clay Cement (LC3): From Laboratory Innovation to Sustainable Industrial Application</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/2071-1050/18/7/3473</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>cement_ccs</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>cement</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>CCS (oxyfuel / post-combustion / LEILAC direct separation)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="19" t="n">
         <v>320</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="15" t="n">
         <v>2028</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="20" t="n">
         <v>0.12</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="20" t="n">
         <v>0.9</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="21" t="n">
         <v>0.408</v>
       </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>IEAGHG 2018 / Heidelberg Materials Brevik CCS 2025</t>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03); Heidelberg Materials (2025), World premiere: CCS cement facility opens in Norway (Brevik CCS)</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
         </is>
       </c>
     </row>
@@ -4863,79 +5839,89 @@
           <t>High alternative-fuel share (biomass / waste-derived kiln fuel)</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="16" t="n">
         <v>165</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="16" t="n">
+      <c r="K10" s="18" t="n">
         <v>0.408</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>IEA/CSI Cement Technology Roadmap 2018</t>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>hvc_ref</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>hvc</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>NG/naphtha steam cracker (reference)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="19" t="n">
         <v>700</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="19" t="n">
         <v>550</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>IEA Future of Petrochemicals 2018</t>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
         </is>
       </c>
     </row>
@@ -4955,79 +5941,89 @@
           <t>Electric steam cracker (e-cracker)</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="16" t="n">
         <v>850</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="16" t="n">
         <v>560</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="14" t="n">
         <v>2030</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>BASF/SABIC/Linde 2024 e-cracker demonstration</t>
+          <t>BASF / SABIC / Linde (2024), Start-up of the world's first large-scale electrically heated steam cracking furnace</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.basf.com/global/en/media/news-releases/2024/04/p-24-177</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>hvc_bio</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>hvc</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Bio-naphtha fed cracker</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="19" t="n">
         <v>720</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="19" t="n">
         <v>620</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="15" t="n">
         <v>2027</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="20" t="n">
         <v>0.15</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="K13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>IEA Future of Petrochemicals 2018 / Material Economics 2019</t>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
         </is>
       </c>
     </row>
@@ -5047,79 +6043,89 @@
           <t>Steam cracker with CCS</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="16" t="n">
         <v>560</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="14" t="n">
         <v>2032</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="17" t="n">
         <v>0.65</v>
       </c>
-      <c r="K14" s="16" t="n">
+      <c r="K14" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>IEAGHG 2018 (industrial CCS costs, applied to chemicals furnaces)</t>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>ammonia_smr</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>ammonia</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Steam methane reforming Haber-Bosch (reference)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="19" t="n">
         <v>650</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>IEA Ammonia Technology Roadmap 2021</t>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
         </is>
       </c>
     </row>
@@ -5139,79 +6145,89 @@
           <t>SMR + CCS (blue ammonia)</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="16" t="n">
         <v>55</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="14" t="n">
         <v>2026</v>
       </c>
-      <c r="I16" s="15" t="n">
+      <c r="I16" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J16" s="15" t="n">
+      <c r="J16" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K16" s="16" t="n">
+      <c r="K16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>IEA Ammonia Technology Roadmap 2021</t>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>ammonia_h2</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>ammonia</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Electrolytic hydrogen Haber-Bosch (green ammonia)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="19" t="n">
         <v>45</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="19" t="n">
         <v>45</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="20" t="n">
         <v>0.15</v>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="19" t="n">
+      <c r="K17" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>IEA Ammonia Technology Roadmap 2021 / Yara Heroya 2024</t>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap - Executive Summary; Yara International (2024), Yara opens renewable hydrogen plant: a major milestone</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap/executive-summary</t>
         </is>
       </c>
     </row>
@@ -5231,79 +6247,89 @@
           <t>Hall-Heroult primary smelting, grid electricity (reference)</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="16" t="n">
         <v>3500</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I18" s="15" t="n">
+      <c r="I18" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="16" t="n">
+      <c r="K18" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>JRC Aluminium factsheet 2026 / IAI 2024</t>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120); International Aluminium Institute (IAI) (2024), Statistics</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>alu_inert</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Inert anode primary smelting (ELYSIS)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="19" t="n">
         <v>3800</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="19" t="n">
         <v>65</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="19" t="n">
         <v>850</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="15" t="n">
         <v>2032</v>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="20" t="n">
         <v>0.15</v>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="19" t="n">
+      <c r="K19" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>ELYSIS 2025 (commercial-size cell) / IEA ETP Guide 2024</t>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>ELYSIS (2025), ELYSIS achieves breakthrough with commercial-size cell</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>https://elysis.com/en/elysis-achieves-breakthrough-with-commercial-size-cell-a-first-in-aluminium-production-using-the</t>
         </is>
       </c>
     </row>
@@ -5323,79 +6349,89 @@
           <t>Secondary (recycled) aluminium, scrap-limited</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="16" t="n">
         <v>750</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H20" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I20" s="15" t="n">
+      <c r="I20" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="16" t="n">
+      <c r="K20" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>Material Economics 2019 / IAI 2024</t>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>glass_ng</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>glass</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Natural-gas fired melting (reference)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="19" t="n">
         <v>120</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="19" t="n">
+      <c r="K21" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>European Commission (CINEA) 2022</t>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
         </is>
       </c>
     </row>
@@ -5415,79 +6451,89 @@
           <t>All-electric melting</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="H22" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I22" s="15" t="n">
+      <c r="I22" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="16" t="n">
+      <c r="K22" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>IEA ETP Clean Energy Technology Guide 2024</t>
+          <t>IEA (2024), ETP Clean Energy Technology Guide (technology readiness levels)</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>glass_hybrid</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>glass</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Hybrid natural-gas / electric / hydrogen melting</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="19" t="n">
         <v>140</v>
       </c>
-      <c r="E23" s="17" t="n">
+      <c r="E23" s="19" t="n">
         <v>8.5</v>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="19" t="n">
         <v>89</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="15" t="n">
         <v>2027</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="19" t="n">
+      <c r="K23" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>IEA ETP Clean Energy Technology Guide 2024</t>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), ETP Clean Energy Technology Guide (technology readiness levels)</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
         </is>
       </c>
     </row>
@@ -5507,79 +6553,89 @@
           <t>Natural-gas CHP process heat (reference)</t>
         </is>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="F24" s="14" t="n">
+      <c r="F24" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="H24" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I24" s="15" t="n">
+      <c r="I24" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="16" t="n">
+      <c r="K24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>CEPI Key Statistics 2022</t>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>paper_elec</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>paper</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>Electrification / high-temperature heat pumps</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="19" t="n">
         <v>280</v>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="19" t="n">
         <v>295</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="15" t="n">
         <v>2027</v>
       </c>
-      <c r="I25" s="18" t="n">
+      <c r="I25" s="20" t="n">
         <v>0.15</v>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="19" t="n">
+      <c r="K25" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>IEA The Future of Heat Pumps 2022</t>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2022), The Future of Heat Pumps</t>
+        </is>
+      </c>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-heat-pumps</t>
         </is>
       </c>
     </row>
@@ -5599,38 +6655,70 @@
           <t>Biomass residues (incl. black liquor) process heat</t>
         </is>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="16" t="n">
         <v>260</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="16" t="n">
         <v>290</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="H26" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="I26" s="15" t="n">
+      <c r="I26" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="16" t="n">
+      <c r="K26" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>IEA Bioenergy 2022 / CEPI Key Statistics 2022</t>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:M26"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5641,12 +6729,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5665,6 +6755,16 @@
           <t>gj_per_t</t>
         </is>
       </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -5677,23 +6777,43 @@
           <t>coal</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="22" t="n">
         <v>7</v>
       </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>steel_bfbof</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>coke</t>
         </is>
       </c>
-      <c r="C3" s="21" t="n">
+      <c r="C3" s="23" t="n">
         <v>11</v>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -5707,23 +6827,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>steel_bfbof</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="23" t="n">
         <v>2</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -5737,23 +6877,43 @@
           <t>coal</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="22" t="n">
         <v>7</v>
       </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>steel_bfbof_ccs</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>coke</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="23" t="n">
         <v>11</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5767,23 +6927,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="22" t="n">
         <v>2.5</v>
       </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>steel_bfbof_ccs</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="23" t="n">
         <v>3</v>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -5797,23 +6977,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="22" t="n">
         <v>7</v>
       </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>steel_ngdri_eaf</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="23" t="n">
         <v>1.5</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -5827,23 +7027,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="22" t="n">
         <v>0.5</v>
       </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>European Parliament (EPRS) (2021), Carbon-free steel production - Cost reduction options and usage of existing gas infrastructure</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/RegData/etudes/STUD/2021/690008/EPRS_STU(2021)690008_EN.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>steel_h2dri_eaf</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="23" t="n">
         <v>6.6</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>European Parliament (EPRS) (2021), Carbon-free steel production - Cost reduction options and usage of existing gas infrastructure</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/RegData/etudes/STUD/2021/690008/EPRS_STU(2021)690008_EN.pdf</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -5857,23 +7077,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="22" t="n">
         <v>2.5</v>
       </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>European Parliament (EPRS) (2021), Carbon-free steel production - Cost reduction options and usage of existing gas infrastructure</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/RegData/etudes/STUD/2021/690008/EPRS_STU(2021)690008_EN.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>steel_scrap_eaf</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="23" t="n">
         <v>0.5</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -5887,23 +7127,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="22" t="n">
         <v>1.7</v>
       </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>cement_ref</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>coal</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="23" t="n">
         <v>2</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -5917,23 +7177,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="22" t="n">
         <v>0.3</v>
       </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>cement_ref</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="23" t="n">
         <v>0.2</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -5947,23 +7227,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="22" t="n">
         <v>0.4</v>
       </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>cement_clinkersub</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>coal</t>
         </is>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="23" t="n">
         <v>1.6</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>MDPI (Sustainability, peer-reviewed) (2026), Limestone Calcined Clay Cement (LC3): From Laboratory Innovation to Sustainable Industrial Application</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/2071-1050/18/7/3473</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -5977,23 +7277,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="22" t="n">
         <v>0.2</v>
       </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>MDPI (Sustainability, peer-reviewed) (2026), Limestone Calcined Clay Cement (LC3): From Laboratory Innovation to Sustainable Industrial Application</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/2071-1050/18/7/3473</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>cement_clinkersub</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="23" t="n">
         <v>0.45</v>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>MDPI (Sustainability, peer-reviewed) (2026), Limestone Calcined Clay Cement (LC3): From Laboratory Innovation to Sustainable Industrial Application</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/2071-1050/18/7/3473</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -6007,23 +7327,43 @@
           <t>coal</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="22" t="n">
         <v>2</v>
       </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>cement_ccs</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="23" t="n">
         <v>0.6</v>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -6037,23 +7377,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="22" t="n">
         <v>0.9</v>
       </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>cement_altfuel</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>biomass</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="23" t="n">
         <v>1.8</v>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -6067,23 +7427,43 @@
           <t>coal</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="22" t="n">
         <v>0.3</v>
       </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>cement_altfuel</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="23" t="n">
         <v>0.1</v>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -6097,23 +7477,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="22" t="n">
         <v>0.45</v>
       </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>hvc_ref</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
+      <c r="C31" s="23" t="n">
         <v>12</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -6127,23 +7527,43 @@
           <t>oil</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>hvc_ref</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="23" t="n">
         <v>1.2</v>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -6157,23 +7577,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="22" t="n">
         <v>1.2</v>
       </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>BASF / SABIC / Linde (2024), Start-up of the world's first large-scale electrically heated steam cracking furnace</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.basf.com/global/en/media/news-releases/2024/04/p-24-177</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>hvc_elec</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="C35" s="21" t="n">
+      <c r="C35" s="23" t="n">
         <v>0.3</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>BASF / SABIC / Linde (2024), Start-up of the world's first large-scale electrically heated steam cracking furnace</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>https://www.basf.com/global/en/media/news-releases/2024/04/p-24-177</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -6187,23 +7627,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="22" t="n">
         <v>11</v>
       </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>BASF / SABIC / Linde (2024), Start-up of the world's first large-scale electrically heated steam cracking furnace</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.basf.com/global/en/media/news-releases/2024/04/p-24-177</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>hvc_bio</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C37" s="21" t="n">
+      <c r="C37" s="23" t="n">
         <v>9</v>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -6217,23 +7677,43 @@
           <t>oil</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C38" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>hvc_bio</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C39" s="21" t="n">
+      <c r="C39" s="23" t="n">
         <v>2</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -6247,23 +7727,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C40" s="20" t="n">
+      <c r="C40" s="22" t="n">
         <v>13.5</v>
       </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>hvc_ccs</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="C41" s="21" t="n">
+      <c r="C41" s="23" t="n">
         <v>1</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -6277,23 +7777,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C42" s="20" t="n">
+      <c r="C42" s="22" t="n">
         <v>2.2</v>
       </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>ammonia_smr</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C43" s="21" t="n">
+      <c r="C43" s="23" t="n">
         <v>29</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -6307,23 +7827,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C44" s="22" t="n">
         <v>0.5</v>
       </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>ammonia_smr_ccs</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C45" s="21" t="n">
+      <c r="C45" s="23" t="n">
         <v>30.5</v>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -6337,23 +7877,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="22" t="n">
         <v>1.2</v>
       </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>ammonia_h2</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="C47" s="21" t="n">
+      <c r="C47" s="23" t="n">
         <v>22</v>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap - Executive Summary</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap/executive-summary</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -6367,23 +7927,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C48" s="20" t="n">
+      <c r="C48" s="22" t="n">
         <v>3</v>
       </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap - Executive Summary</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap/executive-summary</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>alu_ref</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C49" s="23" t="n">
         <v>51</v>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -6397,23 +7977,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C50" s="20" t="n">
+      <c r="C50" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>alu_inert</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C51" s="21" t="n">
+      <c r="C51" s="23" t="n">
         <v>52</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>ELYSIS (2025), ELYSIS achieves breakthrough with commercial-size cell</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>https://elysis.com/en/elysis-achieves-breakthrough-with-commercial-size-cell-a-first-in-aluminium-production-using-the</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -6427,23 +8027,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C52" s="20" t="n">
+      <c r="C52" s="22" t="n">
         <v>0.5</v>
       </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>ELYSIS (2025), ELYSIS achieves breakthrough with commercial-size cell</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>https://elysis.com/en/elysis-achieves-breakthrough-with-commercial-size-cell-a-first-in-aluminium-production-using-the</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>alu_sec</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C53" s="21" t="n">
+      <c r="C53" s="23" t="n">
         <v>2.55</v>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -6457,23 +8077,43 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C54" s="20" t="n">
+      <c r="C54" s="22" t="n">
         <v>1.5</v>
       </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>glass_ng</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C55" s="21" t="n">
+      <c r="C55" s="23" t="n">
         <v>6</v>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -6487,23 +8127,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C56" s="20" t="n">
+      <c r="C56" s="22" t="n">
         <v>0.6</v>
       </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>glass_elec</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C57" s="21" t="n">
+      <c r="C57" s="23" t="n">
         <v>0.3</v>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), ETP Clean Energy Technology Guide (technology readiness levels)</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -6517,23 +8177,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C58" s="20" t="n">
+      <c r="C58" s="22" t="n">
         <v>5.5</v>
       </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), ETP Clean Energy Technology Guide (technology readiness levels)</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>glass_hybrid</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C59" s="21" t="n">
+      <c r="C59" s="23" t="n">
         <v>3</v>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), ETP Clean Energy Technology Guide (technology readiness levels)</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -6547,23 +8227,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C60" s="20" t="n">
+      <c r="C60" s="22" t="n">
         <v>3</v>
       </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), ETP Clean Energy Technology Guide (technology readiness levels)</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>paper_ref</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C61" s="21" t="n">
+      <c r="C61" s="23" t="n">
         <v>8</v>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -6577,23 +8277,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C62" s="20" t="n">
+      <c r="C62" s="22" t="n">
         <v>2</v>
       </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>paper_elec</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C63" s="21" t="n">
+      <c r="C63" s="23" t="n">
         <v>1</v>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2022), The Future of Heat Pumps</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-heat-pumps</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -6607,23 +8327,43 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="C64" s="20" t="n">
+      <c r="C64" s="22" t="n">
         <v>5.5</v>
       </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2022), The Future of Heat Pumps</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-heat-pumps</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>paper_bio</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n">
+      <c r="C65" s="23" t="n">
         <v>0.3</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -6637,27 +8377,115 @@
           <t>biomass</t>
         </is>
       </c>
-      <c r="C66" s="20" t="n">
+      <c r="C66" s="22" t="n">
         <v>9</v>
       </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>paper_bio</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="C67" s="21" t="n">
+      <c r="C67" s="23" t="n">
         <v>2</v>
       </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C67"/>
+  <autoFilter ref="A1:E67"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6668,12 +8496,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6692,6 +8522,16 @@
           <t>price_eur_gj</t>
         </is>
       </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -6699,24 +8539,44 @@
           <t>coal</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C2" s="8" t="n">
         <v>3</v>
       </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>coal</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="12" t="n">
         <v>3</v>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -6725,24 +8585,44 @@
           <t>coal</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>3.1</v>
       </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>coal</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>3.1</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -6751,24 +8631,44 @@
           <t>coal</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>3.2</v>
       </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>coal</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>3.2</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -6777,24 +8677,44 @@
           <t>coke</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>6</v>
       </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>coke</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>6</v>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -6803,24 +8723,44 @@
           <t>coke</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>6.1</v>
       </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>coke</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>6.1</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -6829,24 +8769,44 @@
           <t>coke</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>6.2</v>
       </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>coke</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>6.2</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -6855,24 +8815,44 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>9.5</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -6881,24 +8861,44 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>9</v>
       </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>8.699999999999999</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -6907,24 +8907,44 @@
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>8.5</v>
       </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>natural_gas</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <v>8.300000000000001</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -6933,24 +8953,44 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>24</v>
       </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Eurostat (2024), Electricity price statistics</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B21" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <v>22</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat (2024), Electricity price statistics</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -6959,24 +8999,44 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Eurostat (2024), Electricity price statistics</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="12" t="n">
         <v>20</v>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat (2024), Electricity price statistics</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -6985,24 +9045,44 @@
           <t>electricity</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>19</v>
       </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Eurostat (2024), Electricity price statistics</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="12" t="n">
         <v>18</v>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat (2024), Electricity price statistics</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -7011,24 +9091,44 @@
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), Global Hydrogen Review 2024</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="12" t="n">
         <v>33</v>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), Global Hydrogen Review 2024</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -7037,24 +9137,44 @@
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>28</v>
       </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), Global Hydrogen Review 2024</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B29" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" s="12" t="n">
         <v>25</v>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), Global Hydrogen Review 2024</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -7063,24 +9183,44 @@
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), Global Hydrogen Review 2024</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="12" t="n">
         <v>20</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), Global Hydrogen Review 2024</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -7089,24 +9229,44 @@
           <t>biomass</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>8</v>
       </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>biomass</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C33" s="12" t="n">
         <v>8</v>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -7115,24 +9275,44 @@
           <t>biomass</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>biomass</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="C35" s="12" t="n">
         <v>8.300000000000001</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -7141,24 +9321,44 @@
           <t>biomass</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.4</v>
       </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>biomass</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n">
+      <c r="B37" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="C37" s="12" t="n">
         <v>8.5</v>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -7167,24 +9367,44 @@
           <t>oil</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="14" t="n">
         <v>2025</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>14</v>
       </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n">
+      <c r="B39" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="C39" s="12" t="n">
         <v>14</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -7193,24 +9413,44 @@
           <t>oil</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="14" t="n">
         <v>2035</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>13.8</v>
       </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
+      <c r="B41" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C41" s="11" t="n">
+      <c r="C41" s="12" t="n">
         <v>13.6</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -7219,28 +9459,92 @@
           <t>oil</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="14" t="n">
         <v>2045</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>13.4</v>
       </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C43" s="11" t="n">
+      <c r="C43" s="12" t="n">
         <v>13.2</v>
       </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2024), World Energy Outlook 2024</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C43"/>
+  <autoFilter ref="A1:E43"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7251,13 +9555,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7281,93 +9587,171 @@
           <t>price_high</t>
         </is>
       </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="n">
+      <c r="A2" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="D2" s="14" t="n">
         <v>110</v>
       </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Derived from European Commission (DG CLIMA) (2024), 2040 Climate Target (central path); low/high bands are model-team constructed sensitivity ranges</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="n">
+      <c r="A3" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="15" t="n">
         <v>110</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="15" t="n">
         <v>160</v>
       </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Derived from European Commission (DG CLIMA) (2024), 2040 Climate Target (central path); low/high bands are model-team constructed sensitivity ranges</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="14" t="n">
         <v>2035</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="14" t="n">
         <v>95</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="14" t="n">
         <v>210</v>
       </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Derived from European Commission (DG CLIMA) (2024), 2040 Climate Target (central path); low/high bands are model-team constructed sensitivity ranges</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="15" t="n">
         <v>270</v>
       </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Derived from European Commission (DG CLIMA) (2024), 2040 Climate Target (central path); low/high bands are model-team constructed sensitivity ranges</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="14" t="n">
         <v>2045</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="14" t="n">
         <v>225</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="14" t="n">
         <v>310</v>
       </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Derived from European Commission (DG CLIMA) (2024), 2040 Climate Target (central path); low/high bands are model-team constructed sensitivity ranges</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="15" t="n">
         <v>170</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="15" t="n">
         <v>350</v>
       </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Derived from European Commission (DG CLIMA) (2024), 2040 Climate Target (central path); low/high bands are model-team constructed sensitivity ranges</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:F7"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7378,12 +9762,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7402,6 +9788,16 @@
           <t>tco2_per_gj</t>
         </is>
       </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -7414,23 +9810,43 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="18" t="n">
         <v>0.094</v>
       </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>IPCC (2006), 2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>coke</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C3" s="19" t="n">
+      <c r="C3" s="21" t="n">
         <v>0.107</v>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>IPCC (2006), 2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -7444,23 +9860,43 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="18" t="n">
         <v>0.056</v>
       </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>IPCC (2006), 2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>0</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>IPCC AR6 WGIII (2022), Chapter 11: Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -7474,23 +9910,43 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>IPCC AR6 WGIII (2022), Chapter 11: Industry</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>oil</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>0.073</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>IPCC (2006), 2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -7504,23 +9960,43 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="18" t="n">
         <v>0.065</v>
       </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>European Environment Agency (EEA) (2024), Greenhouse gas emission intensity of electricity generation (indicator)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="21" t="n">
         <v>0.045</v>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>European Environment Agency (EEA) (2024), Greenhouse gas emission intensity of electricity generation (indicator)</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7534,23 +10010,43 @@
           <t>2035</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="18" t="n">
         <v>0.03</v>
       </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>European Environment Agency (EEA) (2024), Greenhouse gas emission intensity of electricity generation (indicator)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="21" t="n">
         <v>0.018</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>European Environment Agency (EEA) (2024), Greenhouse gas emission intensity of electricity generation (indicator)</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -7564,27 +10060,61 @@
           <t>2045</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="18" t="n">
         <v>0.01</v>
       </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>European Environment Agency (EEA) (2024), Greenhouse gas emission intensity of electricity generation (indicator)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>2050</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="21" t="n">
         <v>0.003</v>
       </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>European Environment Agency (EEA) (2024), Greenhouse gas emission intensity of electricity generation (indicator)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:E13"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7595,13 +10125,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7625,6 +10157,16 @@
           <t>value</t>
         </is>
       </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -7637,29 +10179,49 @@
           <t>steel</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="22" t="n">
         <v>0.45</v>
       </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>scrap_share_max</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="D3" s="21" t="n">
+      <c r="D3" s="23" t="n">
         <v>0.47</v>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -7673,29 +10235,49 @@
           <t>steel</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="14" t="n">
         <v>2035</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="22" t="n">
         <v>0.49</v>
       </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>scrap_share_max</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="23" t="n">
         <v>0.51</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -7709,29 +10291,49 @@
           <t>steel</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="14" t="n">
         <v>2045</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="22" t="n">
         <v>0.53</v>
       </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>scrap_share_max</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="23" t="n">
         <v>0.55</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -7745,29 +10347,49 @@
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="22" t="n">
         <v>0.55</v>
       </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>scrap_share_max</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="23" t="n">
         <v>0.58</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7781,29 +10403,49 @@
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="14" t="n">
         <v>2035</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="22" t="n">
         <v>0.6</v>
       </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>scrap_share_max</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="23" t="n">
         <v>0.62</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -7817,29 +10459,49 @@
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="14" t="n">
         <v>2045</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="22" t="n">
         <v>0.64</v>
       </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>scrap_share_max</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>aluminium</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="23" t="n">
         <v>0.65</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -7853,29 +10515,49 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="22" t="n">
         <v>300</v>
       </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>biomass_pj_max</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="23" t="n">
         <v>300</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -7889,29 +10571,49 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="14" t="n">
         <v>2035</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="22" t="n">
         <v>300</v>
       </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>biomass_pj_max</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="23" t="n">
         <v>300</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -7925,29 +10627,49 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="14" t="n">
         <v>2045</v>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="22" t="n">
         <v>300</v>
       </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>biomass_pj_max</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="23" t="n">
         <v>300</v>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -7961,29 +10683,49 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>ccs_mt_max</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="23" t="n">
         <v>5</v>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -7997,29 +10739,49 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="14" t="n">
         <v>2035</v>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="22" t="n">
         <v>20</v>
       </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>ccs_mt_max</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D23" s="23" t="n">
         <v>50</v>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -8033,33 +10795,79 @@
           <t>all</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="14" t="n">
         <v>2045</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="22" t="n">
         <v>80</v>
       </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>ccs_mt_max</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D25" s="23" t="n">
         <v>100</v>
       </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D25"/>
+  <autoFilter ref="A1:F25"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/data/summer-prep-optimization/industry-optimization-inputs.xlsx
+++ b/public/data/summer-prep-optimization/industry-optimization-inputs.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Emission Factors'!$A$1:$E$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Scenarios'!$A$1:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Sources'!$A$1:$G$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Sources'!$A$1:$G$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -628,14 +628,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Scope &amp; geography</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
+          <t>Primary data source</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="140" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Geography: EU-27. Subsectors: steel (crude steel, integrated + EAF routes), cement (clinker-based), high-value chemicals / HVC (steam cracking: ethylene, propylene, aromatics), ammonia, aluminium (primary + secondary), glass (container &amp; flat) and pulp &amp; paper. The subsector/technology/carrier/scenario identifiers used throughout this workbook and the underlying model code are fixed and must not be renamed.</t>
+          <t>The Danish Energy Agency (DEA) Technology Data catalogue series (ens.dk/en/analyses-and-statistics/technology-data) is the primary data source for this model wherever it plausibly covers the underlying equipment: Technology Data for Carbon Capture, Transport and Storage grounds every CCS variant's capture capex, O&amp;M and lifetime; Technology Data for Industrial Process Heat grounds electrification (heat pumps, direct electric firing) and biomass/alternative-fuel process-heat technologies in paper, glass and cement; Technology Data for Renewable Fuels grounds the electrolytic-hydrogen ammonia route and the hydrogen price path used throughout the model. Where DEA genuinely has no coverage — blast-furnace/DRI/EAF steel metallurgy, cement clinker kilns, steam crackers, aluminium smelting, SMR reforming — the pre-existing IEA/IEAGHG/JRC/etc. literature remains primary: DEA is the primary source, not the exclusive one. See the 'sources' sheet for the full register, including a summary row (table=technologies, item=multiple) explaining this policy, and each affected row's 'source' cell for the specific DEA datasheet and conversion used.</t>
         </is>
       </c>
     </row>
@@ -645,14 +645,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="140" customHeight="1">
+          <t>Scope &amp; geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Production &amp; demand: Mt product/yr. CAPEX: EUR per tonne/yr of installed capacity. Fixed OPEX: EUR per tonne/yr of capacity, per year. Variable (non-energy) OPEX: EUR per tonne of product (feedstock, consumables, labour — excludes fuel &amp; carbon cost, which are computed from the energy-use and price tables). Energy use: GJ per tonne of product, by carrier (coal, coke, natural gas, electricity, hydrogen, biomass, oil). Fuel &amp; electricity prices: EUR per GJ (multiply by 3.6 to convert EUR/MWh &lt;-&gt; EUR/GJ for electricity and hydrogen). Carbon price: EUR per tonne of CO2 (EU ETS path). Emission factors: tonnes CO2 per GJ of fuel (combustion factors; the electricity factor is the EU-27 grid emission intensity and varies by year as the grid decarbonises). Process CO2: tonnes CO2 per tonne of product, non-energy chemistry (e.g. limestone calcination in cement, anode consumption in aluminium) not captured by fuel combustion factors. Capture rate: share of a technology's CO2 captured by CCS (0 for technologies without CCS).</t>
+          <t>Geography: EU-27. Subsectors: steel (crude steel, integrated + EAF routes), cement (clinker-based), high-value chemicals / HVC (steam cracking: ethylene, propylene, aromatics), ammonia, aluminium (primary + secondary), glass (container &amp; flat) and pulp &amp; paper. The subsector/technology/carrier/scenario identifiers used throughout this workbook and the underlying model code are fixed and must not be renamed.</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,29 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="140" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Production &amp; demand: Mt product/yr. CAPEX: EUR per tonne/yr of installed capacity. Fixed OPEX: EUR per tonne/yr of capacity, per year. Variable (non-energy) OPEX: EUR per tonne of product (feedstock, consumables, labour — excludes fuel &amp; carbon cost, which are computed from the energy-use and price tables). Energy use: GJ per tonne of product, by carrier (coal, coke, natural gas, electricity, hydrogen, biomass, oil). Fuel &amp; electricity prices: EUR per GJ (multiply by 3.6 to convert EUR/MWh &lt;-&gt; EUR/GJ for electricity and hydrogen). Carbon price: EUR per tonne of CO2 (EU ETS path). Emission factors: tonnes CO2 per GJ of fuel (combustion factors; the electricity factor is the EU-27 grid emission intensity and varies by year as the grid decarbonises). Process CO2: tonnes CO2 per tonne of product, non-energy chemistry (e.g. limestone calcination in cement, anode consumption in aluminium) not captured by fuel combustion factors. Capture rate: share of a technology's CO2 captured by CCS (0 for technologies without CCS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>How the sheets relate</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="180" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="19" ht="180" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>sectors — one row per subsector with 2023 production and direct CO2 anchors.
 demand — the central demand path per subsector and model year (sensitivity scenarios scale this).
@@ -682,35 +699,35 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Per-row sourcing</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="110" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Every data sheet (all except 'sources') carries 'source' and 'source_url' as its last two columns: 'source' is a short citation (Org (Year), Title) and 'source_url' is one working link, wherever possible deep-linking to the exact report or dataset page the number came from (clickable in this sheet). Rows that are genuine modelling choices rather than literature values say so honestly: 'Derived from &lt;source&gt;' for demand paths and the carbon price low/high bands built around a sourced central path, and 'Model assumption (prototype)' for the 13 sensitivity-scenario multipliers in the 'scenarios' sheet, whose source_url points to this model's own README rather than an invented external reference. The 'sources' sheet remains the master register of every citation used, including secondary/cross-check sources not selected as a given row's primary link.</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Per-row sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Every data sheet (all except 'sources') carries 'source' and 'source_url' as its last two columns: 'source' is a short citation (Org (Year), Title) and 'source_url' is one working link, wherever possible deep-linking to the exact report or dataset page the number came from (clickable in this sheet). Rows that are genuine modelling choices rather than literature values say so honestly: 'Derived from &lt;source&gt;' for demand paths and the carbon price low/high bands built around a sourced central path, and 'Model assumption (prototype)' for the 13 sensitivity-scenario multipliers in the 'scenarios' sheet, whose source_url points to this model's own README rather than an invented external reference. The 'sources' sheet remains the master register of every citation used, including secondary/cross-check sources not selected as a given row's primary link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Model &amp; downloads</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>The optimization model itself (Julia + JuMP/HiGHS) lives in the ESABCCMethodHub repo under beta/modules/summer-prep/optimization/model/, in the spirit of the SEAMAPS model (https://github.com/SebastianFra/SEAMAPS). This workbook, the Julia source and the full model bundle (code + data + results + README) are available for download from the 'Summer Prep — Industry Optimization' page of the ESABCC Method Hub.</t>
         </is>
@@ -1172,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1747,32 +1764,32 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>steel_bfbof_ccs</t>
+          <t>steel_ngdri_eaf</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>IEAGHG</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Iron and Steel Technology Roadmap</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Capture-rate and capex premium for BF-BOF + CCUS</t>
+          <t>NG-DRI+EAF energy use and transitional-asset characterisation</t>
         </is>
       </c>
     </row>
@@ -1784,32 +1801,32 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>steel_ngdri_eaf</t>
+          <t>steel_h2dri_eaf</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>European Parliament (EPRS)</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Iron and Steel Technology Roadmap</t>
+          <t>Carbon-free steel production - Cost reduction options and usage of existing gas infrastructure</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+          <t>https://www.europarl.europa.eu/RegData/etudes/STUD/2021/690008/EPRS_STU(2021)690008_EN.pdf</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>NG-DRI+EAF energy use and transitional-asset characterisation</t>
+          <t>H2-DRI+EAF hydrogen intensity (~50-60 kg H2/t) and MAC ~EUR73-166/tCO2 by 2030</t>
         </is>
       </c>
     </row>
@@ -1826,27 +1843,27 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>European Parliament (EPRS)</t>
+          <t>LeadIT (SEI)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Carbon-free steel production - Cost reduction options and usage of existing gas infrastructure</t>
+          <t>Green Steel Tracker</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>https://www.europarl.europa.eu/RegData/etudes/STUD/2021/690008/EPRS_STU(2021)690008_EN.pdf</t>
+          <t>https://www.industrytransition.org/green-steel-tracker/</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>H2-DRI+EAF hydrogen intensity (~50-60 kg H2/t) and MAC ~EUR73-166/tCO2 by 2030</t>
+          <t>Commercial availability timeline (first plants building now)</t>
         </is>
       </c>
     </row>
@@ -1858,32 +1875,32 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>steel_h2dri_eaf</t>
+          <t>steel_scrap_eaf</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>LeadIT (SEI)</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Green Steel Tracker</t>
+          <t>Iron and Steel Technology Roadmap</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>https://www.industrytransition.org/green-steel-tracker/</t>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Commercial availability timeline (first plants building now)</t>
+          <t>Scrap-EAF as mature, low direct-CO2 route</t>
         </is>
       </c>
     </row>
@@ -1900,27 +1917,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>Material Economics</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Iron and Steel Technology Roadmap</t>
+          <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Scrap-EAF as mature, low direct-CO2 route</t>
+          <t>Scrap availability as the binding long-run constraint on secondary steel</t>
         </is>
       </c>
     </row>
@@ -1932,32 +1949,32 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>steel_scrap_eaf</t>
+          <t>cement_ref</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Material Economics</t>
+          <t>IEA / CSI</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+          <t>Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Scrap availability as the binding long-run constraint on secondary steel</t>
+          <t>Reference kiln thermal energy (~3.4 GJ/t clinker) and clinker-ratio-driven process CO2 (0.53 tCO2/t clinker x 0.77 ratio)</t>
         </is>
       </c>
     </row>
@@ -1969,32 +1986,32 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>cement_ref</t>
+          <t>cement_clinkersub</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>IEA / CSI</t>
+          <t>MDPI (Sustainability, peer-reviewed)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+          <t>Limestone Calcined Clay Cement (LC3): From Laboratory Innovation to Sustainable Industrial Application</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+          <t>https://www.mdpi.com/2071-1050/18/7/3473</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Reference kiln thermal energy (~3.4 GJ/t clinker) and clinker-ratio-driven process CO2 (0.53 tCO2/t clinker x 0.77 ratio)</t>
+          <t>LC3 clinker replacement up to ~50%, ~40% CO2 cut, near-cost-neutral</t>
         </is>
       </c>
     </row>
@@ -2006,32 +2023,32 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>cement_clinkersub</t>
+          <t>cement_ccs</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>MDPI (Sustainability, peer-reviewed)</t>
+          <t>Heidelberg Materials</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Limestone Calcined Clay Cement (LC3): From Laboratory Innovation to Sustainable Industrial Application</t>
+          <t>World premiere: CCS cement facility opens in Norway (Brevik CCS)</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2071-1050/18/7/3473</t>
+          <t>https://www.heidelbergmaterials.com/en/pr-2025-06-18</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>LC3 clinker replacement up to ~50%, ~40% CO2 cut, near-cost-neutral</t>
+          <t>First industrial-scale cement CCS operational since 2025; available_from calibrated to this</t>
         </is>
       </c>
     </row>
@@ -2043,22 +2060,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>cement_ccs</t>
+          <t>cement_altfuel</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>IEAGHG</t>
+          <t>IEA / CSI</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2068,7 +2085,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>MAC EUR30-107/tCO2 avoided; capture rate ~90% assumed for post-combustion</t>
+          <t>Alternative-fuel co-processing mature and widely deployed</t>
         </is>
       </c>
     </row>
@@ -2080,32 +2097,32 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>cement_ccs</t>
+          <t>hvc_ref</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Heidelberg Materials</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>World premiere: CCS cement facility opens in Norway (Brevik CCS)</t>
+          <t>The Future of Petrochemicals</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>https://www.heidelbergmaterials.com/en/pr-2025-06-18</t>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>First industrial-scale cement CCS operational since 2025; available_from calibrated to this</t>
+          <t>Reference steam-cracker furnace energy intensity order of magnitude</t>
         </is>
       </c>
     </row>
@@ -2117,32 +2134,32 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>cement_altfuel</t>
+          <t>hvc_elec</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>IEA / CSI</t>
+          <t>BASF / SABIC / Linde</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+          <t>Start-up of the world's first large-scale electrically heated steam cracking furnace</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+          <t>https://www.basf.com/global/en/media/news-releases/2024/04/p-24-177</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Alternative-fuel co-processing mature and widely deployed</t>
+          <t>Electric cracker demonstration; furnace CO2 cut up to ~90%</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2171,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>hvc_ref</t>
+          <t>hvc_bio</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2179,7 +2196,7 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Reference steam-cracker furnace energy intensity order of magnitude</t>
+          <t>Bio-naphtha as drop-in feedstock displacing fossil naphtha</t>
         </is>
       </c>
     </row>
@@ -2191,32 +2208,32 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>hvc_elec</t>
+          <t>ammonia_smr</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>BASF / SABIC / Linde</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Start-up of the world's first large-scale electrically heated steam cracking furnace</t>
+          <t>Ammonia Technology Roadmap</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>https://www.basf.com/global/en/media/news-releases/2024/04/p-24-177</t>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Electric cracker demonstration; furnace CO2 cut up to ~90%</t>
+          <t>Reference SMR-Haber-Bosch natural gas intensity ~28-32 GJ/t NH3</t>
         </is>
       </c>
     </row>
@@ -2228,32 +2245,32 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>hvc_bio</t>
+          <t>ammonia_h2</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>Yara International</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>The Future of Petrochemicals</t>
+          <t>Yara opens renewable hydrogen plant: a major milestone</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+          <t>https://www.yara.com/corporate-releases/yara-opens-renewable-hydrogen-plant-a-major-milestone/</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Bio-naphtha as drop-in feedstock displacing fossil naphtha</t>
+          <t>First commercial green-ammonia plant (Heroya) inaugurated 2024; calibrates available_from</t>
         </is>
       </c>
     </row>
@@ -2265,32 +2282,32 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>hvc_ccs</t>
+          <t>alu_ref</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>IEAGHG</t>
+          <t>JRC (European Commission)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Aluminium factsheet (JRC144120)</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Industrial CCS cost/capture-rate benchmarks applied to chemicals furnaces (moderate capture, dilute flue gas)</t>
+          <t>Direct anode process CO2 ~1.4 tCO2/t primary Al implied by ~2.75 Mt / ~2 Mt production</t>
         </is>
       </c>
     </row>
@@ -2302,32 +2319,32 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>ammonia_smr</t>
+          <t>alu_ref</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>International Aluminium Institute (IAI)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Ammonia Technology Roadmap</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+          <t>https://international-aluminium.org/statistics/</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Reference SMR-Haber-Bosch natural gas intensity ~28-32 GJ/t NH3</t>
+          <t>Primary smelting electricity intensity ~14-15 MWh/t (~51 GJ/t)</t>
         </is>
       </c>
     </row>
@@ -2339,32 +2356,32 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ammonia_smr_ccs</t>
+          <t>alu_inert</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>ELYSIS</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Ammonia Technology Roadmap</t>
+          <t>ELYSIS achieves breakthrough with commercial-size cell</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+          <t>https://elysis.com/en/elysis-achieves-breakthrough-with-commercial-size-cell-a-first-in-aluminium-production-using-the</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Blue-ammonia (SMR/ATR+CCS) capture rate and capex premium</t>
+          <t>Full-scale 450 kA commercial-size inert-anode cell started up Nov 2025; eliminates direct process CO2</t>
         </is>
       </c>
     </row>
@@ -2376,32 +2393,32 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>ammonia_h2</t>
+          <t>alu_sec</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>Material Economics</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Ammonia Technology Roadmap - Executive Summary</t>
+          <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/ammonia-technology-roadmap/executive-summary</t>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Electrolytic-H2 ammonia MAC ~US$820/t NH3 (~US$400/t above conventional); needs power &lt;~US$40/MWh for parity</t>
+          <t>Secondary aluminium uses ~5% of primary smelting energy; scrap-supply constrained</t>
         </is>
       </c>
     </row>
@@ -2413,32 +2430,32 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ammonia_h2</t>
+          <t>glass_ng</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Yara International</t>
+          <t>European Commission (CINEA)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Yara opens renewable hydrogen plant: a major milestone</t>
+          <t>How LIFE is reducing emissions from glass production</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>https://www.yara.com/corporate-releases/yara-opens-renewable-hydrogen-plant-a-major-milestone/</t>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>First commercial green-ammonia plant (Heroya) inaugurated 2024; calibrates available_from</t>
+          <t>Reference gas-fired melting energy ~5-7 GJ/t and process CO2 from carbonate raw materials</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2467,32 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>alu_ref</t>
+          <t>glass_elec</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>JRC (European Commission)</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Aluminium factsheet (JRC144120)</t>
+          <t>ETP Clean Energy Technology Guide (technology readiness levels)</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Direct anode process CO2 ~1.4 tCO2/t primary Al implied by ~2.75 Mt / ~2 Mt production</t>
+          <t>All-electric melting TRL and availability</t>
         </is>
       </c>
     </row>
@@ -2487,22 +2504,22 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>alu_ref</t>
+          <t>glass_hybrid</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>International Aluminium Institute (IAI)</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>ETP Clean Energy Technology Guide (technology readiness levels)</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>https://international-aluminium.org/statistics/</t>
+          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2512,7 +2529,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Primary smelting electricity intensity ~14-15 MWh/t (~51 GJ/t)</t>
+          <t>Large hybrid furnace TRL 6-8, emerging</t>
         </is>
       </c>
     </row>
@@ -2524,118 +2541,118 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>alu_inert</t>
+          <t>paper_ref</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>ELYSIS</t>
+          <t>CEPI</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>ELYSIS achieves breakthrough with commercial-size cell</t>
+          <t>Key Statistics 2022 - European pulp &amp; paper industry</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>https://elysis.com/en/elysis-achieves-breakthrough-with-commercial-size-cell-a-first-in-aluminium-production-using-the</t>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Full-scale 450 kA commercial-size inert-anode cell started up Nov 2025; eliminates direct process CO2</t>
+          <t>Reference fossil process-heat intensity order of magnitude</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>technologies</t>
+          <t>fuel_prices</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>alu_sec</t>
+          <t>coal</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Material Economics</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+          <t>World Energy Outlook 2024</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Secondary aluminium uses ~5% of primary smelting energy; scrap-supply constrained</t>
+          <t>Steam coal industrial price path, central scenario order of magnitude ~EUR3/GJ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>technologies</t>
+          <t>fuel_prices</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>glass_ng</t>
+          <t>coke</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>European Commission (CINEA)</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>How LIFE is reducing emissions from glass production</t>
+          <t>World Energy Outlook 2024</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Reference gas-fired melting energy ~5-7 GJ/t and process CO2 from carbonate raw materials</t>
+          <t>Metallurgical coke priced at a premium to thermal coal (~2x)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>technologies</t>
+          <t>fuel_prices</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>glass_elec</t>
+          <t>natural_gas</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2645,12 +2662,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>ETP Clean Energy Technology Guide (technology readiness levels)</t>
+          <t>World Energy Outlook 2024</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -2660,34 +2677,34 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>All-electric melting TRL and availability</t>
+          <t>EU industrial natural gas price path, central scenario, declining from ~EUR10/GJ (2025)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>technologies</t>
+          <t>fuel_prices</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>glass_hybrid</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>ETP Clean Energy Technology Guide (technology readiness levels)</t>
+          <t>Electricity price statistics</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -2697,34 +2714,34 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Large hybrid furnace TRL 6-8, emerging</t>
+          <t>EU-27 industrial electricity price ~EUR24/GJ (~EUR86/MWh) in 2025, declining as renewables share rises</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>technologies</t>
+          <t>fuel_prices</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>paper_ref</t>
+          <t>biomass</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>CEPI</t>
+          <t>IEA Bioenergy</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Key Statistics 2022 - European pulp &amp; paper industry</t>
+          <t>Decarbonizing industrial process heat: the role of biomass</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2734,19 +2751,19 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Reference fossil process-heat intensity order of magnitude</t>
+          <t>Solid biomass/residue fuel price order of magnitude ~EUR8/GJ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>technologies</t>
+          <t>fuel_prices</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>paper_elec</t>
+          <t>oil</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -2756,271 +2773,271 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>The Future of Heat Pumps</t>
+          <t>World Energy Outlook 2024</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/the-future-of-heat-pumps</t>
+          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Industrial heat-pump electrification of process heat; TRL and availability</t>
+          <t>Industrial oil/naphtha price path, central scenario order of magnitude ~EUR14/GJ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>technologies</t>
+          <t>carbon_price</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>paper_bio</t>
+          <t>eu_ets</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>IEA Bioenergy</t>
+          <t>European Commission (DG CLIMA)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Decarbonizing industrial process heat: the role of biomass</t>
+          <t>2040 Climate Target</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Biomass/black-liquor process heat, commercially mature</t>
+          <t>Central EU ETS price path ~EUR80/t (2025) rising to ~EUR200/t (2040) and ~EUR250/t (2050); low/high bands constructed around this by the model team, consistent with the range of EC impact-assessment and market-forward modelling</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>fuel_prices</t>
+          <t>carbon_price</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>coal</t>
+          <t>eu_ets</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>ICAP</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>World Energy Outlook 2024</t>
+          <t>EU Emissions Trading System (EU ETS)</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+          <t>https://icapcarbonaction.com/en/ets/eu-emissions-trading-system-eu-ets</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>Steam coal industrial price path, central scenario order of magnitude ~EUR3/GJ</t>
+          <t>Historical and current EUA price context used to anchor the 2025 starting point</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>fuel_prices</t>
+          <t>emission_factors</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>coke</t>
+          <t>coal</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IPCC</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>World Energy Outlook 2024</t>
+          <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Metallurgical coke priced at a premium to thermal coal (~2x)</t>
+          <t>Default combustion emission factor for coal, ~94 kgCO2/GJ</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>fuel_prices</t>
+          <t>emission_factors</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>natural_gas</t>
+          <t>coke</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IPCC</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>World Energy Outlook 2024</t>
+          <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>EU industrial natural gas price path, central scenario, declining from ~EUR10/GJ (2025)</t>
+          <t>Default combustion emission factor for coke oven coke, ~107 kgCO2/GJ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>fuel_prices</t>
+          <t>emission_factors</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>natural_gas</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>IPCC</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Electricity price statistics</t>
+          <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Electricity_price_statistics</t>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>EU-27 industrial electricity price ~EUR24/GJ (~EUR86/MWh) in 2025, declining as renewables share rises</t>
+          <t>Default combustion emission factor for natural gas, ~56 kgCO2/GJ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>fuel_prices</t>
+          <t>emission_factors</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>oil</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IPCC</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Global Hydrogen Review 2024</t>
+          <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>Low-carbon hydrogen cost path ~EUR40/GJ (~EUR4.8/kg) in 2025 falling to ~EUR20/GJ (~EUR2.4/kg) by 2050</t>
+          <t>Default combustion emission factor for gas/diesel oil &amp; naphtha, ~73 kgCO2/GJ</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>fuel_prices</t>
+          <t>emission_factors</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>biomass</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>IEA Bioenergy</t>
+          <t>IPCC AR6 WGIII</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Decarbonizing industrial process heat: the role of biomass</t>
+          <t>Chapter 11: Industry</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+          <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -3030,71 +3047,71 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Solid biomass/residue fuel price order of magnitude ~EUR8/GJ</t>
+          <t>Zero combustion CO2 for hydrogen; upstream emissions depend on production route (not modelled at combustion stage)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>fuel_prices</t>
+          <t>emission_factors</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>oil</t>
+          <t>biomass</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IPCC AR6 WGIII</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>World Energy Outlook 2024</t>
+          <t>Chapter 11: Industry</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/world-energy-outlook-2024</t>
+          <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Industrial oil/naphtha price path, central scenario order of magnitude ~EUR14/GJ</t>
+          <t>Biomass combustion CO2 conventionally reported as zero at point of combustion (biogenic carbon accounting); land-use/supply-chain emissions not modelled here</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>carbon_price</t>
+          <t>emission_factors</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>eu_ets</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>European Commission (DG CLIMA)</t>
+          <t>European Environment Agency (EEA)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>2040 Climate Target</t>
+          <t>Greenhouse gas emission intensity of electricity generation (indicator)</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/topics/climate-action/eu-climate-energy-and-environmental-targets/2040-targets_en</t>
+          <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -3104,404 +3121,404 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>Central EU ETS price path ~EUR80/t (2025) rising to ~EUR200/t (2040) and ~EUR250/t (2050); low/high bands constructed around this by the model team, consistent with the range of EC impact-assessment and market-forward modelling</t>
+          <t>EU-27 grid emission factor ~0.065 tCO2/GJ (~230 gCO2/kWh) in 2025 falling to ~0.003 tCO2/GJ by 2050 as the grid decarbonises</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>carbon_price</t>
+          <t>constraints</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>eu_ets</t>
+          <t>scrap_share_max</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>ICAP</t>
+          <t>Material Economics</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>EU Emissions Trading System (EU ETS)</t>
+          <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/ets/eu-emissions-trading-system-eu-ets</t>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>Historical and current EUA price context used to anchor the 2025 starting point</t>
+          <t>Steel scrap availability rising from ~45% (2025) to ~55% (2050) of demand servable by scrap-EAF; aluminium secondary share rising ~55% to ~65%, both circularity-constrained</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>emission_factors</t>
+          <t>constraints</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>coal</t>
+          <t>biomass_pj_max</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>IPCC</t>
+          <t>JRC (European Commission)</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
+          <t>Brief on biomass for energy in the European Union</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Default combustion emission factor for coal, ~94 kgCO2/GJ</t>
+          <t>Sustainable biomass availability for industrial energy use constrained to an order-of-magnitude ceiling of ~300 PJ/yr across all EU-27 industry</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>emission_factors</t>
+          <t>constraints</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>coke</t>
+          <t>ccs_mt_max</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>IPCC</t>
+          <t>Global CCS Institute</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
+          <t>Global Status of CCS report series</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
+          <t>https://www.globalccsinstitute.com/</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Default combustion emission factor for coke oven coke, ~107 kgCO2/GJ</t>
+          <t>EU CO2 transport &amp; storage network ramp-up: ~0 Mt/yr (2025) to ~100 Mt/yr (2050) capturable across all subsectors</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>emission_factors</t>
+          <t>constraints</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>natural_gas</t>
+          <t>ccs_mt_max</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>IPCC</t>
+          <t>Clean Air Task Force</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
+          <t>Carbon capture and storage in Europe: slow but significant progress in 2025</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
+          <t>https://www.catf.us/2025/11/carbon-capture-storage-europe-slow-but-significant-progress-2025/</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Default combustion emission factor for natural gas, ~56 kgCO2/GJ</t>
+          <t>Status of first EU CO2 storage/transport projects (Northern Lights, Porthos, Greensand) calibrating the near-term ramp</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>emission_factors</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>oil</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>IPCC</t>
+          <t>Eurofer</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>2006 IPCC Guidelines for National Greenhouse Gas Inventories, Vol. 2 (Energy)</t>
+          <t>European Steel in Figures 2024</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/vol2.html</t>
+          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Default combustion emission factor for gas/diesel oil &amp; naphtha, ~73 kgCO2/GJ</t>
+          <t>Demand path assumed broadly flat-to-declining from the 2023 production base</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>emission_factors</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>cement</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>IPCC AR6 WGIII</t>
+          <t>Cembureau</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Chapter 11: Industry</t>
+          <t>Key Facts &amp; Figures</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
+          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>Zero combustion CO2 for hydrogen; upstream emissions depend on production route (not modelled at combustion stage)</t>
+          <t>Demand path assumed broadly flat-to-declining from the 2023 production base</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>emission_factors</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>biomass</t>
+          <t>aluminium</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>IPCC AR6 WGIII</t>
+          <t>International Aluminium Institute (IAI)</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Chapter 11: Industry</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
+          <t>https://international-aluminium.org/statistics/</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Biomass combustion CO2 conventionally reported as zero at point of combustion (biogenic carbon accounting); land-use/supply-chain emissions not modelled here</t>
+          <t>Demand path assumed slight growth, reflecting continued electrification-driven aluminium demand</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>emission_factors</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>hvc</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>European Environment Agency (EEA)</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Greenhouse gas emission intensity of electricity generation (indicator)</t>
+          <t>The Future of Petrochemicals</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>https://www.eea.europa.eu/en/analysis/indicators/greenhouse-gas-emission-intensity-of-1</t>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>EU-27 grid emission factor ~0.065 tCO2/GJ (~230 gCO2/kWh) in 2025 falling to ~0.003 tCO2/GJ by 2050 as the grid decarbonises</t>
+          <t>Demand path assumed slight growth</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>constraints</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>scrap_share_max</t>
+          <t>discount_rate</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Material Economics</t>
+          <t>IPCC</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+          <t>AR6 WGIII, Chapter 11: Industry</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+          <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Steel scrap availability rising from ~45% (2025) to ~55% (2050) of demand servable by scrap-EAF; aluminium secondary share rising ~55% to ~65%, both circularity-constrained</t>
+          <t>7% social/industry discount rate and capital recovery factor approach used to annualise CAPEX, consistent with standard industrial decarbonisation cost-modelling practice</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>constraints</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>biomass_pj_max</t>
+          <t>ammonia</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>JRC (European Commission)</t>
+          <t>Fertilizers Europe</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Brief on biomass for energy in the European Union</t>
+          <t>Fertilizer Industry Facts and Figures 2023 edition</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Sustainable biomass availability for industrial energy use constrained to an order-of-magnitude ceiling of ~300 PJ/yr across all EU-27 industry</t>
+          <t>Demand path assumed broadly flat-to-slightly-declining from the 2023 production base</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>constraints</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>ccs_mt_max</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Global CCS Institute</t>
+          <t>FEVE (European Container Glass Federation)</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Global Status of CCS report series</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>https://www.globalccsinstitute.com/</t>
+          <t>https://feve.org/about-glass/statistics/</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
@@ -3511,108 +3528,108 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>EU CO2 transport &amp; storage network ramp-up: ~0 Mt/yr (2025) to ~100 Mt/yr (2050) capturable across all subsectors</t>
+          <t>Demand path assumed broadly flat from the 2023 production base</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>constraints</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>ccs_mt_max</t>
+          <t>paper</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Clean Air Task Force</t>
+          <t>CEPI</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+          <t>Key Statistics 2022 - European pulp &amp; paper industry</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>https://www.catf.us/2025/11/carbon-capture-storage-europe-slow-but-significant-progress-2025/</t>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Status of first EU CO2 storage/transport projects (Northern Lights, Porthos, Greensand) calibrating the near-term ramp</t>
+          <t>Demand path assumed gently declining from the 2023 production base</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>scenarios</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Eurofer</t>
+          <t>ESABCC Method Hub (model team)</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>European Steel in Figures 2024</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>https://www.eurofer.eu/publications/brochures-booklets-and-factsheets/european-steel-in-figures-2024</t>
+          <t>Model README - sensitivity scenario methodology</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Demand path assumed broadly flat-to-declining from the 2023 production base</t>
+          <t>All 13 scenarios (1 central + 12 sensitivities) are prototype modelling assumptions (parameter multipliers applied to already-sourced central inputs), not independent literature values; see the README for the full methodology and per-scenario definitions.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>cement</t>
+          <t>steel_bfbof_ccs</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Cembureau</t>
+          <t>Danish Energy Agency</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Key Facts &amp; Figures</t>
+          <t>Technology Data for Carbon Capture, Transport and Storage</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>https://www.cembureau.eu/media/00ejjcfj/key-facts-figures-publication-june-2024.pdf</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -3622,34 +3639,34 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Demand path assumed broadly flat-to-declining from the 2023 production base</t>
+          <t>Sheet 401.c (post-combustion capture, cement-kiln flue gas, used as CO2-concentration proxy for BF-BOF top gas): specific investment, fixed/var O&amp;M per tCO2 captured, 25-yr capture-unit lifetime; now the primary source, replacing the generic IEAGHG (2018) estimate.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>aluminium</t>
+          <t>cement_ccs</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>International Aluminium Institute (IAI)</t>
+          <t>Danish Energy Agency</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Technology Data for Carbon Capture, Transport and Storage</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>https://international-aluminium.org/statistics/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -3659,44 +3676,44 @@
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Demand path assumed slight growth, reflecting continued electrification-driven aluminium demand</t>
+          <t>Sheet 401.c (post-combustion capture retrofit, 4500 t clinker/day cement kiln - a direct technology match): specific investment, fixed/var O&amp;M per tCO2 captured, 25-yr capture-unit lifetime; now the primary source, replacing the generic IEAGHG (2018) estimate. Heidelberg Materials retained for available_from calibration.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>hvc</t>
+          <t>cement_altfuel</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>Danish Energy Agency</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>The Future of Petrochemicals</t>
+          <t>Technology Data for Industrial Process Heat</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>Demand path assumed slight growth</t>
+          <t>Sheet 7.2 (direct firing of solid fuels, 100% net efficiency) used as the closest available DEA proxy for alternative/biomass kiln-fuel firing; DEA has no cement-kiln-specific alt-fuel sheet, so IEA/CSI (2018) is retained for kiln-level capex/opex/lifetime, with DEA as the primary technical cross-check per the model's DEA-primary-source policy.</t>
         </is>
       </c>
     </row>
@@ -3708,59 +3725,59 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>discount_rate</t>
+          <t>hvc_elec</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>IPCC</t>
+          <t>Danish Energy Agency</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>AR6 WGIII, Chapter 11: Industry</t>
+          <t>Technology Data for Industrial Process Heat</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>https://www.ipcc.ch/report/ar6/wg3/chapter/chapter-11/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>7% social/industry discount rate and capital recovery factor approach used to annualise CAPEX, consistent with standard industrial decarbonisation cost-modelling practice</t>
+          <t>Sheet 7.3 (direct electric firing, 100% net efficiency, up to 2000 degC) confirms electrified cracking-furnace heat supply is well within DEA's technical envelope; DEA prices heating elements only, so BASF/SABIC/Linde (2024) is retained for full e-cracker capex/opex/lifetime, with DEA as the primary technical cross-check per the model's DEA-primary-source policy.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>ammonia</t>
+          <t>hvc_ccs</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Fertilizers Europe</t>
+          <t>Danish Energy Agency</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Fertilizer Industry Facts and Figures 2023 edition</t>
+          <t>Technology Data for Carbon Capture, Transport and Storage</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>https://www.fertilizerseurope.com/publications/fertilizers-industry-facts-and-figures-2023-edition/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -3770,34 +3787,34 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Demand path assumed broadly flat-to-slightly-declining from the 2023 production base</t>
+          <t>Sheet 401.a (post-combustion capture, dilute ~15% CO2 CHP/biomass flue gas, used as proxy for cracker-furnace flue gas - DEA has no HVC-specific sheet): specific investment, fixed/var O&amp;M per tCO2 captured, 25-yr capture-unit lifetime; now the primary source, replacing the generic IEAGHG (2018) estimate.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>glass</t>
+          <t>ammonia_smr_ccs</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>FEVE (European Container Glass Federation)</t>
+          <t>Danish Energy Agency</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Technology Data for Carbon Capture, Transport and Storage</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>https://feve.org/about-glass/statistics/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -3807,86 +3824,345 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Demand path assumed broadly flat from the 2023 production base</t>
+          <t>Sheet 401.c (post-combustion capture, cement-kiln flue gas used as moderate-CO2-concentration proxy - DEA has no SMR/ammonia-specific sheet): specific investment, fixed/var O&amp;M per tCO2 captured, 25-yr capture-unit lifetime; now the primary source, replacing the IEA (2021) Ammonia Technology Roadmap-implied capture premium.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>paper</t>
+          <t>ammonia_h2</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>CEPI</t>
+          <t>Danish Energy Agency</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Key Statistics 2022 - European pulp &amp; paper industry</t>
+          <t>Technology Data for Renewable Fuels</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Demand path assumed gently declining from the 2023 production base</t>
+          <t>Sheet 5.4 (Hydrogen to Ammonia, Haber-Bosch synthesis excl. electrolyser and excl. ASU): specific investment, fixed/var O&amp;M, 30-yr lifetime; now the primary source. Correctly excludes electrolyser capex, which is already reflected in the purchased-hydrogen carrier price (see fuel_prices,hydrogen below), avoiding the double-counting implicit in the prior IEA (2021) Ammonia Technology Roadmap Executive Summary bundled estimate. Yara International (2024) retained for available_from calibration.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>scenarios</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
+          <t>glass_elec</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Sheet 7.3 (direct electric firing: 100% net efficiency, up to 2000 degC, 20-yr technical lifetime) confirms all-electric glass melting is well within DEA's technical envelope and grounds the updated 20-yr lifetime; DEA prices heating elements only (not furnace shell/refractories/forming equipment), so IEA (2024) ETP is retained for furnace-level capex/opex, with DEA as the primary technical cross-check per the model's DEA-primary-source policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>technologies</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>glass_hybrid</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Blend of sheet 7.3 (direct electric firing) and sheet 6.1 (gas/oil boiler) as proxies for the electric and gas-fired shares of a hybrid furnace; grounds the updated 18-yr lifetime. DEA prices heating elements/burners only, so IEA (2024) ETP is retained for furnace-level capex/opex, with DEA as the primary technical cross-check per the model's DEA-primary-source policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>technologies</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>paper_elec</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Sheet 2.a (high-temperature heat pump up to 125 degC): COP 2.7-2.95 (2025-2050), 1.15 M EUR/MW nominal investment (2030 est.), 20-yr technical lifetime; now the primary source, replacing IEA (2022) Future of Heat Pumps as the quantitative basis for capex, electricity intensity and lifetime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>technologies</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>paper_bio</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Sheet 6.2 (biomass boiler): 88.9% annual-average efficiency, 0.878 M EUR/MW nominal investment (2025), 25-yr technical lifetime; now the primary source, replacing IEA Bioenergy (2022) as the quantitative basis for capex, fuel intensity and lifetime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>fuel_prices</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>hydrogen</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Technology Data for Renewable Fuels</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Sheet 1.1 (alkaline electrolysis, AEC, 100 MW plant): bottom-up levelised cost of hydrogen from DEA electrolyser capex (975-&gt;300 EUR/kW, 2025-&gt;2050), 4%/yr fixed O&amp;M, 25-yr lifetime (7% WACC CRF), DEA stack+BOP electricity consumption (56.7-&gt;47.6 kWh/kg H2), 8000 full-load h/yr, and this model's own Eurostat electricity price path; now the primary source, replacing the IEA (2024) Global Hydrogen Review market-price path, which this bottom-up calculation shows was materially more optimistic (17-40% below the DEA-grounded figure, widening over the horizon).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>fuel_prices</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Technology Data for Generation of Electricity and District Heat</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-generation-electricity-and-district-heating</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Reviewed as a possible source for the industrial electricity price path but not adopted: this DEA catalogue prices generation technologies (LCOE), not the retail/industrial electricity price this table needs, so Eurostat market-price statistics remain the more appropriate and directly applicable source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>fuel_prices</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>biomass</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Technology Data for Renewable Fuels</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>Reviewed as a possible source for the biomass feedstock price path but not adopted: this DEA catalogue prices biomass-conversion plant technologies (boilers, gasifiers, pyrolysis), not EU biomass feedstock market prices, so the IEA Bioenergy feedstock-price estimate is retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>technologies</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>ESABCC Method Hub (model team)</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>Model README - sensitivity scenario methodology</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>beta/modules/summer-prep/optimization/model/README.md</t>
-        </is>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
-        <is>
-          <t>All 13 scenarios (1 central + 12 sensitivities) are prototype modelling assumptions (parameter multipliers applied to already-sourced central inputs), not independent literature values; see the README for the full methodology and per-scenario definitions.</t>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Technology Data catalogue series (Industrial Process Heat; Carbon Capture, Transport and Storage; Renewable Fuels; Generation of Electricity and District Heat)</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>2024-2026</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Per explicit user direction, the DEA Technology Data catalogue series is the primary source for this model wherever it plausibly covers the underlying equipment (all CCS variants; paper/glass/HVC electrification and biomass/alt-fuel heat; electrolytic-hydrogen ammonia synthesis and the hydrogen price path). Where DEA genuinely has no coverage (BF-BOF/DRI/EAF steel process metallurgy, cement clinker kilns, steam crackers, aluminium smelting, SMR reforming), the pre-existing IEA/IEAGHG/JRC/etc. sources remain primary - DEA is primary, not exclusive, consistent with data-quality requirements.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G73"/>
+  <autoFilter ref="A1:G80"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -3951,14 +4227,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5483,13 +5766,13 @@
         </is>
       </c>
       <c r="D3" s="19" t="n">
-        <v>650</v>
+        <v>770</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>25</v>
@@ -5508,12 +5791,12 @@
       </c>
       <c r="L3" s="11" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage (sheet 401.c, post-combustion capture retrofit, cement kiln flue gas used as CO2-concentration proxy for BF-BOF flue/top gas, ~90% capture); converted at 1.185 tCO2 captured/t steel (combustion CO2 at 0.6 capture rate), 8000 full-load h/yr, DEA specific investment 2.5 M EUR/(tCO2/h) (2030) -&gt; capture add-on 370 EUR/(t/yr) added to unchanged base steel_bfbof capex (400); base process still IEA (2020) Iron and Steel Technology Roadmap. DEA capture-retrofit benchmark implies a materially higher capture add-on than the prior generic IEAGHG (2018) estimate (250 EUR/t) - adopted the DEA-grounded (higher, more conservative) figure and retained it for fixed/var O&amp;M add-ons (11.9 and 3.0 EUR/t respectively, close to the prior estimate).</t>
         </is>
       </c>
       <c r="M3" s="13" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -5789,16 +6072,16 @@
         </is>
       </c>
       <c r="D9" s="19" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E9" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="G9" s="15" t="n">
         <v>25</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>35</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>30</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>2028</v>
@@ -5814,12 +6097,12 @@
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03); Heidelberg Materials (2025), World premiere: CCS cement facility opens in Norway (Brevik CCS)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage (sheet 401.c, post-combustion capture retrofit for a 4500 t clinker/day cement kiln - a direct match for this technology); converted at 0.567 tCO2 captured/t clinker (0.9 capture rate on ~0.63 tCO2/t pre-capture process+combustion CO2), 8000 full-load h/yr, DEA specific investment 2.5 M EUR/(tCO2/h) (2030) -&gt; capture add-on ~177 EUR/(t/yr) on top of the unchanged cement_ref kiln capex (150), materially consistent with the prior implied add-on (170 EUR/t from IEAGHG 2018); fixed/var O&amp;M add-ons recomputed from DEA (5.7 and 1.4 EUR/t) and are lower than the prior generic IEAGHG estimate - adopted the DEA, more granular, figures. Capture-unit lifetime (25 yr per DEA) now governs over the kiln's own 35-yr structural life, since capture equipment would need reinvestment first. Heidelberg Materials (2025) Brevik CCS start-up retained for the available_from=2028 calibration.</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -5865,12 +6148,12 @@
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 7.2, direct firing of solid fuels: 100% net efficiency, used as the closest available DEA proxy for alternative/biomass fuel firing in a cement kiln burner - DEA has no cement-kiln-specific alt-fuel sheet). Capex/fixed/var opex and the 35-yr lifetime retained from IEA / CSI (2018) Technology Roadmap: Low-Carbon Transition in the Cement Industry: DEA's burner-only figures (0.258 M EUR/MW, 15-yr burner lifetime) price the firing equipment alone, not the rotary kiln shell/refractories/preheater that dominate cement-kiln capex and govern its much longer structural life - divergence noted, fuller-scope IEA/CSI figures kept.</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -5967,12 +6250,12 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>BASF / SABIC / Linde (2024), Start-up of the world's first large-scale electrically heated steam cracking furnace</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 7.3, direct electric firing: 100% net efficiency, heat supply up to 2000 degC, technically consistent with electrically heated cracking-furnace tube temperatures ~850 degC). Capex/fixed/var opex and the 30-yr lifetime retained from BASF / SABIC / Linde (2024)'s e-cracker demonstration: DEA's sheet prices resistive heating elements alone (~0.07 M EUR/MW, converting to a small fraction of this technology's capex) and excludes the cracker tubes, compressors and separation train that dominate real e-cracker capex - a wide divergence, noted, with the fuller-scope BASF-anchored literature figure kept as the defensible capex/opex/lifetime.</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>https://www.basf.com/global/en/media/news-releases/2024/04/p-24-177</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -6044,16 +6327,16 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>900</v>
+        <v>1020</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H14" s="14" t="n">
         <v>2032</v>
@@ -6069,12 +6352,12 @@
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage (sheet 401.a, post-combustion capture retrofit on a dilute ~15% CO2 CHP/biomass flue gas, used as the closest available DEA proxy for cracker-furnace flue gas - DEA has no HVC/steam-cracker-specific capture sheet); converted at 0.539 tCO2 captured/t HVC (0.65 capture rate on ~0.83 tCO2/t pre-capture combustion CO2), 8000 full-load h/yr, DEA specific investment 4.8 M EUR/(tCO2/h) (2030, higher than the cement-kiln stream because dilute flue gas costs more per tCO2 captured) -&gt; capture add-on ~324 EUR/(t/yr) on top of the unchanged hvc_ref cracker capex (700); this is materially higher than the prior generic IEAGHG (2018) add-on (200 EUR/t) - adopted the DEA-grounded (higher) figure as the more defensible, dilute-stream-consistent estimate. Fixed O&amp;M add-on similarly raised (9.4 vs 5 EUR/t); variable O&amp;M add-on (DEA solvent/consumable cost only, 1.4 EUR/t) is well below the prior generic estimate (10 EUR/t) so a smaller blended reduction was applied (560-&gt;555) to avoid understating broader non-energy consumable costs DEA does not price.</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -6146,13 +6429,13 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>900</v>
+        <v>1020</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>25</v>
@@ -6171,12 +6454,12 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>IEA (2021), Ammonia Technology Roadmap</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage (sheet 401.c, post-combustion capture on cement-kiln-like moderate-concentration flue gas, used as the closest available DEA proxy - DEA has no SMR/ammonia-specific capture sheet); converted at 1.025 tCO2 captured/t NH3 (0.6 capture rate on ~1.71 tCO2/t pre-capture reformer flue-gas CO2), 8000 full-load h/yr, DEA specific investment ~2.9 M EUR/(tCO2/h) (2025/26) -&gt; capture add-on ~372 EUR/(t/yr) on top of the unchanged ammonia_smr capex (650); materially higher than the prior IEA (2021) Ammonia Technology Roadmap-implied add-on (250 EUR/t) - adopted the DEA-grounded (higher) figure. Fixed O&amp;M add-on (10.9 EUR/t) closely matches the prior estimate (10 EUR/t, minimal change); variable O&amp;M add-on (DEA solvent-only, 2.6 EUR/t) is well below the prior generic estimate (15 EUR/t) so a smaller blended reduction was applied (55-&gt;45) to avoid understating catalyst/other non-energy variable costs DEA does not price for this route.</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -6197,16 +6480,16 @@
         </is>
       </c>
       <c r="D17" s="19" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>2026</v>
@@ -6222,12 +6505,12 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>IEA (2021), Ammonia Technology Roadmap - Executive Summary; Yara International (2024), Yara opens renewable hydrogen plant: a major milestone</t>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels (sheet 5.4, Hydrogen to Ammonia, Haber-Bosch synthesis excl. electrolyser and excl. ASU); converted at 18.9 GJ/t NH3 specific energy content, 8000 full-load h/yr, DEA specific investment ~1.5 M EUR/MW NH3 output (2025/26 interpolated) -&gt; 1000 EUR/(t/yr), notably lower than the prior IEA (2021) Ammonia Technology Roadmap Executive Summary estimate (1500 EUR/t): the DEA sheet deliberately excludes the electrolyser, whose capex is already reflected in the purchased-hydrogen carrier price (fuel_prices.csv) - the prior 1500 EUR/t figure double-counted electrolyser capex once via the H2 price and once via plant capex; the DEA synthesis-only figure corrects this. Fixed O&amp;M similarly reduced (45-&gt;30 EUR/t/yr, DEA ~46 k EUR/MW/yr converted); variable O&amp;M retained close to the prior estimate (45-&gt;40 EUR/t) since DEA's synthesis-only variable cost (0.11 EUR/t) excludes the air-separation-unit (ASU/N2 supply) consumables that dominate green-ammonia non-energy variable cost. Lifetime raised to 30 yr (DEA HB-synthesis plant lifetime) from 20 yr. Yara International (2024) Heroya plant retained for the available_from=2026 calibration.</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/ammonia-technology-roadmap/executive-summary</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6744,7 @@
         <v>88</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H22" s="14" t="n">
         <v>2025</v>
@@ -6477,12 +6760,12 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>IEA (2024), ETP Clean Energy Technology Guide (technology readiness levels)</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 7.3, direct electric firing: 100% net efficiency, heat supply up to 2000 degC by 2030, 20-yr technical lifetime) - confirms all-electric glass melting is thermally and technically well within DEA's direct-electric-firing envelope. Capex/fixed/var opex retained from IEA (2024) ETP Clean Energy Technology Guide (150/9/88 EUR/t): DEA's sheet prices the resistive heating elements alone (~0.07 M EUR/MW, which converts to only ~13 EUR/(t/yr) at this technology's energy intensity) and does not include the furnace shell, refractories, batch/feeding and forming equipment that dominate a full electric-melter rebuild cost - a wide (&gt;10x) divergence versus furnace-level literature estimates, so the fuller-scope IEA figure was kept as the defensible capex/opex. Lifetime raised from 15 to 20 yr per DEA's direct-electric-firing technical lifetime.</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6795,7 @@
         <v>89</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>2027</v>
@@ -6528,12 +6811,12 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>IEA (2024), ETP Clean Energy Technology Guide (technology readiness levels)</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (blend of sheet 7.3 direct electric firing, up to 2000 degC, 20-yr lifetime, and sheet 6.1 gas/oil boiler, 94% efficiency, 25-yr lifetime, as proxies for the electric and gas-fired shares of a hybrid furnace). Capex/fixed/var opex retained from IEA (2024) ETP Clean Energy Technology Guide (140/8.5/89 EUR/t): as with glass_elec, DEA's per-MW figures price heating elements/burners only, not a full hybrid furnace rebuild - the wide divergence is noted and the fuller-scope literature figure was kept. Lifetime raised from 15 to 18 yr, a blended estimate between the DEA electric (20 yr) and gas (25 yr) equipment lifetimes and the shorter real-world furnace campaign life typical of hybrid melters.</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/data-and-statistics/data-tools/etp-clean-energy-technology-guide</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -6605,10 +6888,10 @@
         </is>
       </c>
       <c r="D25" s="19" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F25" s="19" t="n">
         <v>295</v>
@@ -6630,12 +6913,12 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>IEA (2022), The Future of Heat Pumps</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 2.a, high-temperature heat pump up to 125 degC); converted at 7.5 GJ/t useful process heat (from the unchanged paper_ref 8 GJ/t natural-gas input at 94% DEA boiler efficiency, sheet 6.1), 8000 full-load h/yr, DEA nominal investment 1.15 M EUR/MW (2030 est., since available_from=2027) -&gt; 300 EUR/(t/yr), consistent with the prior IEA (2022) Future of Heat Pumps estimate (280 EUR/t). Fixed O&amp;M retained at ~7% of capex (21 EUR/t/yr) since DEA's equipment-only fixed O&amp;M (EUR2456/MW/yr, ~0.2% of capex) reflects heat-pump unit maintenance only, not the mill's broader fixed operating cost; variable O&amp;M unchanged (295 EUR/t) for the same reason. Lifetime (20 yr) matches the prior estimate exactly.</t>
         </is>
       </c>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/the-future-of-heat-pumps</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -6656,10 +6939,10 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>290</v>
@@ -6681,12 +6964,12 @@
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 6.2, biomass boiler); converted at 7.5 GJ/t useful process heat and 88.9% DEA annual-average boiler efficiency -&gt; 8.5 GJ/t biomass fuel input (down slightly from the prior 9 GJ/t IEA Bioenergy estimate), 8000 full-load h/yr, DEA nominal investment 0.878 M EUR/MW (2025) -&gt; 230 EUR/(t/yr), down from the prior 260 EUR/t. Fixed O&amp;M partially adopted (20-&gt;16 EUR/t/yr): DEA's boiler-only fixed O&amp;M (converted, ~10 EUR/t/yr) omits solid-biomass handling, storage and ash-removal costs that are material for this fuel, so a blended value above the pure DEA figure was retained. Variable O&amp;M unchanged (290 EUR/t, dominated by broader mill non-energy variable costs DEA's boiler-only figure - ~3 EUR/t - does not capture). Lifetime (25 yr) matches the prior estimate exactly.</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -6882,12 +7165,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -6907,12 +7190,12 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -6932,12 +7215,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -6957,12 +7240,12 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7615,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7357,12 +7640,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7382,12 +7665,12 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7732,12 +8015,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7757,12 +8040,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7782,12 +8065,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>IEAGHG (2018), Cost of CO2 capture in the industrial sector: cement and iron &amp; steel industries (2018-TR03)</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>https://ieaghg.org/publications/cost-of-co2-capture-in-the-industrial-sector-cement-and-iron-and-steel-industries/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7857,12 +8140,12 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>IEA (2021), Ammonia Technology Roadmap</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7882,12 +8165,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>IEA (2021), Ammonia Technology Roadmap</t>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage - capture-penalty energy use cross-checked against DEA sheet 401.c/401.a heat and electricity input per tCO2 captured and found consistent with this pre-existing figure; retained unchanged.</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
         </is>
       </c>
     </row>
@@ -7907,12 +8190,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>IEA (2021), Ammonia Technology Roadmap - Executive Summary</t>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels (sheet 5.4, 0.18 t H2/t NH3 at ~120 GJ/t H2 LHV = 21.6 GJ/t, consistent with this pre-existing 22 GJ/t figure) - retained.</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/ammonia-technology-roadmap/executive-summary</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
     </row>
@@ -7932,7 +8215,7 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>IEA (2021), Ammonia Technology Roadmap - Executive Summary</t>
+          <t>IEA (2021), Ammonia Technology Roadmap - Executive Summary - retained: DEA sheet 5.4 explicitly excludes the air-separation unit (ASU) that this electricity mainly serves, so it is outside DEA's scope here.</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -8307,12 +8590,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>IEA (2022), The Future of Heat Pumps</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 2.a note: steam generation reduces heat-pump COP) - retained unchanged as high-temperature steam trim allowance.</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/the-future-of-heat-pumps</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -8328,16 +8611,16 @@
         </is>
       </c>
       <c r="C64" s="22" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>IEA (2022), The Future of Heat Pumps</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 2.a, high-temperature heat pump, COP 2.8 at 2030 est.); 7.5 GJ/t useful heat / COP 2.8 = 2.7 GJ/t for heat supply, plus 2.0 GJ/t unchanged baseline (non-heat) electricity = 4.7 GJ/t total, down from the prior 5.5 GJ/t IEA estimate reflecting DEA's documented heat-pump COP.</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/the-future-of-heat-pumps</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -8357,12 +8640,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 6.2) - retained unchanged as start-up/trim allowance.</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -8378,16 +8661,16 @@
         </is>
       </c>
       <c r="C66" s="22" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 6.2, biomass boiler, 88.9% annual-average efficiency); 7.5 GJ/t useful heat / 0.889 = 8.4-8.5 GJ/t fuel input, down slightly from the prior 9 GJ/t IEA Bioenergy estimate.</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8690,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>IEA Bioenergy (2022), Decarbonizing industrial process heat: the role of biomass</t>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat (sheet 6.2, auxiliary electricity ~2% of heat gen) - retained unchanged.</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>https://www.ieabioenergy.com/blog/publications/decarbonizing-industrial-process-heat-the-role-of-biomass/</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
         </is>
       </c>
     </row>
@@ -9095,16 +9378,16 @@
         <v>2025</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>IEA (2024), Global Hydrogen Review 2024</t>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels (sheet 1.1, alkaline electrolysis AEC, 100 MW plant) - levelised cost of hydrogen built bottom-up from DEA electrolyser capex (975-&gt;300 EUR/kW, 2025-&gt;2050), 4%/yr fixed O&amp;M, 25-yr lifetime (7% WACC CRF), DEA stack+BOP electricity consumption (56.7-&gt;47.6 kWh/kg H2), 8000 full-load h/yr, and this table's own Eurostat electricity price path; replaces the prior IEA (2024) Global Hydrogen Review market-price path, which this bottom-up DEA calculation shows was materially more optimistic (17-40% below the DEA-grounded figure across the horizon, widening over time) - the DEA figure is adopted as the more transparent, reproducible, EU-specific estimate.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
     </row>
@@ -9118,16 +9401,16 @@
         <v>2030</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>IEA (2024), Global Hydrogen Review 2024</t>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels (sheet 1.1, alkaline electrolysis AEC, 100 MW plant) - levelised cost of hydrogen built bottom-up from DEA electrolyser capex (975-&gt;300 EUR/kW, 2025-&gt;2050), 4%/yr fixed O&amp;M, 25-yr lifetime (7% WACC CRF), DEA stack+BOP electricity consumption (56.7-&gt;47.6 kWh/kg H2), 8000 full-load h/yr, and this table's own Eurostat electricity price path; replaces the prior IEA (2024) Global Hydrogen Review market-price path, which this bottom-up DEA calculation shows was materially more optimistic (17-40% below the DEA-grounded figure across the horizon, widening over time) - the DEA figure is adopted as the more transparent, reproducible, EU-specific estimate.</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
     </row>
@@ -9141,16 +9424,16 @@
         <v>2035</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>IEA (2024), Global Hydrogen Review 2024</t>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels (sheet 1.1, alkaline electrolysis AEC, 100 MW plant) - levelised cost of hydrogen built bottom-up from DEA electrolyser capex (975-&gt;300 EUR/kW, 2025-&gt;2050), 4%/yr fixed O&amp;M, 25-yr lifetime (7% WACC CRF), DEA stack+BOP electricity consumption (56.7-&gt;47.6 kWh/kg H2), 8000 full-load h/yr, and this table's own Eurostat electricity price path; replaces the prior IEA (2024) Global Hydrogen Review market-price path, which this bottom-up DEA calculation shows was materially more optimistic (17-40% below the DEA-grounded figure across the horizon, widening over time) - the DEA figure is adopted as the more transparent, reproducible, EU-specific estimate.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
     </row>
@@ -9164,16 +9447,16 @@
         <v>2040</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>IEA (2024), Global Hydrogen Review 2024</t>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels (sheet 1.1, alkaline electrolysis AEC, 100 MW plant) - levelised cost of hydrogen built bottom-up from DEA electrolyser capex (975-&gt;300 EUR/kW, 2025-&gt;2050), 4%/yr fixed O&amp;M, 25-yr lifetime (7% WACC CRF), DEA stack+BOP electricity consumption (56.7-&gt;47.6 kWh/kg H2), 8000 full-load h/yr, and this table's own Eurostat electricity price path; replaces the prior IEA (2024) Global Hydrogen Review market-price path, which this bottom-up DEA calculation shows was materially more optimistic (17-40% below the DEA-grounded figure across the horizon, widening over time) - the DEA figure is adopted as the more transparent, reproducible, EU-specific estimate.</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
     </row>
@@ -9187,16 +9470,16 @@
         <v>2045</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>IEA (2024), Global Hydrogen Review 2024</t>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels (sheet 1.1, alkaline electrolysis AEC, 100 MW plant) - levelised cost of hydrogen built bottom-up from DEA electrolyser capex (975-&gt;300 EUR/kW, 2025-&gt;2050), 4%/yr fixed O&amp;M, 25-yr lifetime (7% WACC CRF), DEA stack+BOP electricity consumption (56.7-&gt;47.6 kWh/kg H2), 8000 full-load h/yr, and this table's own Eurostat electricity price path; replaces the prior IEA (2024) Global Hydrogen Review market-price path, which this bottom-up DEA calculation shows was materially more optimistic (17-40% below the DEA-grounded figure across the horizon, widening over time) - the DEA figure is adopted as the more transparent, reproducible, EU-specific estimate.</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
     </row>
@@ -9210,16 +9493,16 @@
         <v>2050</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>IEA (2024), Global Hydrogen Review 2024</t>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels (sheet 1.1, alkaline electrolysis AEC, 100 MW plant) - levelised cost of hydrogen built bottom-up from DEA electrolyser capex (975-&gt;300 EUR/kW, 2025-&gt;2050), 4%/yr fixed O&amp;M, 25-yr lifetime (7% WACC CRF), DEA stack+BOP electricity consumption (56.7-&gt;47.6 kWh/kg H2), 8000 full-load h/yr, and this table's own Eurostat electricity price path; replaces the prior IEA (2024) Global Hydrogen Review market-price path, which this bottom-up DEA calculation shows was materially more optimistic (17-40% below the DEA-grounded figure across the horizon, widening over time) - the DEA figure is adopted as the more transparent, reproducible, EU-specific estimate.</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>https://www.iea.org/reports/global-hydrogen-review-2024</t>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
         </is>
       </c>
     </row>

--- a/public/data/summer-prep-optimization/industry-optimization-inputs.xlsx
+++ b/public/data/summer-prep-optimization/industry-optimization-inputs.xlsx
@@ -11,25 +11,27 @@
     <sheet name="Sectors" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Demand" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Technologies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Energy Use" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Fuel Prices" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Carbon Price" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Emission Factors" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Scenarios" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Sources" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Capex Trajectory" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Energy Use" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Fuel Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Carbon Price" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Emission Factors" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Constraints" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Scenarios" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Sources" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sectors'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Demand'!$A$1:$E$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Technologies'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Energy Use'!$A$1:$E$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fuel Prices'!$A$1:$E$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Carbon Price'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Emission Factors'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$F$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Scenarios'!$A$1:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Sources'!$A$1:$G$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Capex Trajectory'!$A$1:$F$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Energy Use'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fuel Prices'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Carbon Price'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Emission Factors'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Constraints'!$A$1:$F$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Scenarios'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Sources'!$A$1:$G$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -575,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -618,7 +620,7 @@
     <row r="7" ht="110" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>This workbook is the input dataset for a SEAMAPS-style least-cost optimization model of EU-27 energy-intensive industry, covering seven subsectors (steel, cement, high-value chemicals, ammonia, aluminium, glass, pulp &amp; paper), 25 production technologies, seven energy carriers and six model years (2025-2050, 5-year steps). The model minimises total discounted system cost (CAPEX + fixed &amp; variable OPEX + fuel + carbon cost) subject to demand, capacity, technology-availability, build-rate, scrap-availability, biomass and CCS-storage constraints, and is re-solved across 13 scenarios (1 central case + 12 sensitivities) to test how results respond to carbon-price, CAPEX, demand, electricity, hydrogen, efficiency and deployment-speed assumptions.</t>
+          <t>This workbook is the input dataset for a SEAMAPS-style least-cost optimization model of EU-27 energy-intensive industry, covering seven subsectors (steel, cement, high-value chemicals, ammonia, aluminium, glass, pulp &amp; paper), 25 production technologies, seven energy carriers and six model years (2025-2050, 5-year steps). The model minimises total discounted system cost (CAPEX + fixed &amp; variable OPEX + fuel + carbon cost) subject to demand, capacity, technology-availability, build-rate, scrap-availability, biomass and CCS-storage constraints, and is re-solved across 15 scenarios (1 central case + 14 sensitivities) to test how results respond to carbon-price, CAPEX, demand, electricity, hydrogen, efficiency, technology-learning-speed and deployment-speed assumptions.</t>
         </is>
       </c>
     </row>
@@ -628,14 +630,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Primary data source</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="140" customHeight="1">
+          <t>Time-dependent technology CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="230" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>The Danish Energy Agency (DEA) Technology Data catalogue series (ens.dk/en/analyses-and-statistics/technology-data) is the primary data source for this model wherever it plausibly covers the underlying equipment: Technology Data for Carbon Capture, Transport and Storage grounds every CCS variant's capture capex, O&amp;M and lifetime; Technology Data for Industrial Process Heat grounds electrification (heat pumps, direct electric firing) and biomass/alternative-fuel process-heat technologies in paper, glass and cement; Technology Data for Renewable Fuels grounds the electrolytic-hydrogen ammonia route and the hydrogen price path used throughout the model. Where DEA genuinely has no coverage — blast-furnace/DRI/EAF steel metallurgy, cement clinker kilns, steam crackers, aluminium smelting, SMR reforming — the pre-existing IEA/IEAGHG/JRC/etc. literature remains primary: DEA is the primary source, not the exclusive one. See the 'sources' sheet for the full register, including a summary row (table=technologies, item=multiple) explaining this policy, and each affected row's 'source' cell for the specific DEA datasheet and conversion used.</t>
+          <t>Technology CAPEX is no longer a single flat number: the 'Capex Trajectory' sheet gives each of the 25 technologies a full 2025-2050 cost PATH (5-yr steps), and every technology's 2025 value matches its 'technologies' sheet CAPEX exactly (the model's base year is unchanged). Three families of evidence ground these paths. (1) DEA-covered clean technologies (all four CCS variants, plus paper electrification/biomass, glass electrification/hybrid, HVC electrification and green-ammonia synthesis): the relevant Danish Energy Agency Technology Data datasheet publishes 2025-2050 specific/nominal investment figures; the RELATIVE decline SHAPE from that sheet (2035/2045 linearly interpolated where the sheet skips them) is applied to the technology's own 2025 capex anchor. For the CCS variants specifically, the DEA shape is applied only to the capture add-on portion of capex (the base process capex, itself a mature reference technology, is held flat). Several DEA proxy sheets (direct electric/solid-fuel firing) show NO decline over 2025-2050 for the heating-element/burner equipment they price, so those technologies' trajectories are flat by DEA evidence, not by default - see each row's 'basis' cell. (2) Non-DEA clean technologies (H2-DRI+EAF steel, NG-DRI+EAF, inert-anode aluminium, LC3 clinker substitution, bio-naphtha cracking) use one-factor learning-rate literature (IRENA 2020 for electrolysis-adjacent equipment, Rubin et al. 2015's general learning-rate meta-analysis for novel-process/mature-process-kit bands), translated into an annual decline under an explicit, documented EU capacity-doublings assumption. (3) Mature reference/incumbent technologies (BF-BOF, conventional cement/HVC/ammonia, primary/secondary aluminium, gas-fired glass, gas-fired paper, scrap-EAF) are held flat: no learning is claimed without a source to support it. Two new sensitivity scenarios (learning_fast / learning_slow, see below) let the model test faster or slower realisations of these cost-decline paths.</t>
         </is>
       </c>
     </row>
@@ -645,14 +647,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Scope &amp; geography</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="70" customHeight="1">
+          <t>Primary data source</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="140" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Geography: EU-27. Subsectors: steel (crude steel, integrated + EAF routes), cement (clinker-based), high-value chemicals / HVC (steam cracking: ethylene, propylene, aromatics), ammonia, aluminium (primary + secondary), glass (container &amp; flat) and pulp &amp; paper. The subsector/technology/carrier/scenario identifiers used throughout this workbook and the underlying model code are fixed and must not be renamed.</t>
+          <t>The Danish Energy Agency (DEA) Technology Data catalogue series (ens.dk/en/analyses-and-statistics/technology-data) is the primary data source for this model wherever it plausibly covers the underlying equipment: Technology Data for Carbon Capture, Transport and Storage grounds every CCS variant's capture capex, O&amp;M and lifetime; Technology Data for Industrial Process Heat grounds electrification (heat pumps, direct electric firing) and biomass/alternative-fuel process-heat technologies in paper, glass and cement; Technology Data for Renewable Fuels grounds the electrolytic-hydrogen ammonia route and the hydrogen price path used throughout the model. Where DEA genuinely has no coverage — blast-furnace/DRI/EAF steel metallurgy, cement clinker kilns, steam crackers, aluminium smelting, SMR reforming — the pre-existing IEA/IEAGHG/JRC/etc. literature remains primary: DEA is the primary source, not the exclusive one. See the 'sources' sheet for the full register, including a summary row (table=technologies, item=multiple) explaining this policy, and each affected row's 'source' cell for the specific DEA datasheet and conversion used.</t>
         </is>
       </c>
     </row>
@@ -662,14 +664,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="140" customHeight="1">
+          <t>Scope &amp; geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Production &amp; demand: Mt product/yr. CAPEX: EUR per tonne/yr of installed capacity. Fixed OPEX: EUR per tonne/yr of capacity, per year. Variable (non-energy) OPEX: EUR per tonne of product (feedstock, consumables, labour — excludes fuel &amp; carbon cost, which are computed from the energy-use and price tables). Energy use: GJ per tonne of product, by carrier (coal, coke, natural gas, electricity, hydrogen, biomass, oil). Fuel &amp; electricity prices: EUR per GJ (multiply by 3.6 to convert EUR/MWh &lt;-&gt; EUR/GJ for electricity and hydrogen). Carbon price: EUR per tonne of CO2 (EU ETS path). Emission factors: tonnes CO2 per GJ of fuel (combustion factors; the electricity factor is the EU-27 grid emission intensity and varies by year as the grid decarbonises). Process CO2: tonnes CO2 per tonne of product, non-energy chemistry (e.g. limestone calcination in cement, anode consumption in aluminium) not captured by fuel combustion factors. Capture rate: share of a technology's CO2 captured by CCS (0 for technologies without CCS).</t>
+          <t>Geography: EU-27. Subsectors: steel (crude steel, integrated + EAF routes), cement (clinker-based), high-value chemicals / HVC (steam cracking: ethylene, propylene, aromatics), ammonia, aluminium (primary + secondary), glass (container &amp; flat) and pulp &amp; paper. The subsector/technology/carrier/scenario identifiers used throughout this workbook and the underlying model code are fixed and must not be renamed.</t>
         </is>
       </c>
     </row>
@@ -679,40 +681,41 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="140" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Production &amp; demand: Mt product/yr. CAPEX: EUR per tonne/yr of installed capacity. Fixed OPEX: EUR per tonne/yr of capacity, per year. Variable (non-energy) OPEX: EUR per tonne of product (feedstock, consumables, labour — excludes fuel &amp; carbon cost, which are computed from the energy-use and price tables). Energy use: GJ per tonne of product, by carrier (coal, coke, natural gas, electricity, hydrogen, biomass, oil). Fuel &amp; electricity prices: EUR per GJ (multiply by 3.6 to convert EUR/MWh &lt;-&gt; EUR/GJ for electricity and hydrogen). Carbon price: EUR per tonne of CO2 (EU ETS path). Emission factors: tonnes CO2 per GJ of fuel (combustion factors; the electricity factor is the EU-27 grid emission intensity and varies by year as the grid decarbonises). Process CO2: tonnes CO2 per tonne of product, non-energy chemistry (e.g. limestone calcination in cement, anode consumption in aluminium) not captured by fuel combustion factors. Capture rate: share of a technology's CO2 captured by CCS (0 for technologies without CCS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>How the sheets relate</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="180" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22" ht="210" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>sectors — one row per subsector with 2023 production and direct CO2 anchors.
 demand — the central demand path per subsector and model year (sensitivity scenarios scale this).
-technologies — one row per production technology (25 total) with CAPEX/OPEX/lifetime/availability/build-rate/capture-rate/process-CO2 parameters.
+technologies — one row per production technology (25 total) with 2025 CAPEX/OPEX/lifetime/availability/build-rate/capture-rate/process-CO2 parameters.
+capex_trajectory — the same 25 technologies' CAPEX over time (2025-2050, 5-yr steps): each row's 2025 value matches the technologies sheet exactly, and the 'basis' column documents the DEA datasheet or learning-rate literature and computation behind every later year.
 energy_use — long-format specific energy use (GJ/t) by technology and carrier; every technology's non-zero carriers appear here.
 fuel_prices — EUR/GJ price path per carrier and year.
 carbon_price — EU ETS low/central/high EUR/tCO2 path.
 emission_factors — combustion emission factors per carrier (constant carriers use year='all'; electricity varies by year as the EU grid decarbonises).
 constraints — scrap-availability ceilings (steel, aluminium), the economy-wide biomass ceiling and the CO2 transport &amp; storage ramp ceiling.
-scenarios — the 13 scenario definitions (1 central + 12 sensitivities) as multiplier-based parameter shocks.
+scenarios — the 15 scenario definitions (1 central + 14 sensitivities) as multiplier-based parameter shocks, including the two new learning_fast / learning_slow scenarios that scale the capex_trajectory decline exponent (capex(t,y) = capex(t,2025) x r(t,y)^factor, factor=1.5/0.5) to test faster/slower technology-learning realisations.
 sources — the full provenance table: every headline number traced to a real, cited organisation, report and URL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Per-row sourcing</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="110" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Every data sheet (all except 'sources') carries 'source' and 'source_url' as its last two columns: 'source' is a short citation (Org (Year), Title) and 'source_url' is one working link, wherever possible deep-linking to the exact report or dataset page the number came from (clickable in this sheet). Rows that are genuine modelling choices rather than literature values say so honestly: 'Derived from &lt;source&gt;' for demand paths and the carbon price low/high bands built around a sourced central path, and 'Model assumption (prototype)' for the 13 sensitivity-scenario multipliers in the 'scenarios' sheet, whose source_url points to this model's own README rather than an invented external reference. The 'sources' sheet remains the master register of every citation used, including secondary/cross-check sources not selected as a given row's primary link.</t>
         </is>
       </c>
     </row>
@@ -722,12 +725,29 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>Per-row sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Every data sheet (all except 'sources') carries 'source' and 'source_url' as its last two columns: 'source' is a short citation (Org (Year), Title) and 'source_url' is one working link, wherever possible deep-linking to the exact report or dataset page the number came from (clickable in this sheet). Rows that are genuine modelling choices rather than literature values say so honestly: 'Derived from &lt;source&gt;' for demand paths and the carbon price low/high bands built around a sourced central path, and 'Model assumption (prototype)' for the 14 sensitivity-scenario multipliers in the 'scenarios' sheet, whose source_url points to this model's own README rather than an invented external reference. The 'sources' sheet remains the master register of every citation used, including secondary/cross-check sources not selected as a given row's primary link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>Model &amp; downloads</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>The optimization model itself (Julia + JuMP/HiGHS) lives in the ESABCCMethodHub repo under beta/modules/summer-prep/optimization/model/, in the spirit of the SEAMAPS model (https://github.com/SebastianFra/SEAMAPS). This workbook, the Julia source and the full model bundle (code + data + results + README) are available for download from the 'Summer Prep — Industry Optimization' page of the ESABCC Method Hub.</t>
         </is>
@@ -744,7 +764,760 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D2" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D3" s="23" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>aluminium</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>aluminium</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>aluminium</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>aluminium</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>aluminium</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>scrap_share_max</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>aluminium</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>biomass_pj_max</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>biomass_pj_max</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>biomass_pj_max</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>biomass_pj_max</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>biomass_pj_max</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>biomass_pj_max</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D19" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>ccs_mt_max</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>ccs_mt_max</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>ccs_mt_max</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>ccs_mt_max</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ccs_mt_max</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>80</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>ccs_mt_max</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.globalccsinstitute.com/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F25"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1177,19 +1950,79 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>learning_fast</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Technology learning accelerates: 2025-&gt;2050 capex decline exponent x1.5 (deeper cost cuts for clean tech)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>learning_rate</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>learning_slow</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Technology learning slows: 2025-&gt;2050 capex decline exponent x0.5 (learning stalls)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>learning_rate</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Model assumption (prototype)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4161,8 +4994,304 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>capex_trajectory</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>steel_h2dri_eaf</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>IRENA</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>Electrolysis-adjacent one-factor learning-rate band (16-21% per doubling for electrolysers/fuel cells) applied to H2-DRI+EAF's 2025-2050 capex trajectory (18% LR x ~2 assumed EU capacity doublings, ~33% total decline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>capex_trajectory</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>alu_inert</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>IRENA</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Electrolysis-adjacent one-factor learning-rate band (lower end of 16-21%) applied to inert-anode primary aluminium smelting's 2025-2050 capex trajectory (15% LR x ~2 assumed EU capacity doublings, ~28% total decline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>capex_trajectory</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>steel_h2dri_eaf</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>DIW Berlin</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Revisiting Investment Costs for Green Steel (Discussion Paper 2082)</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>https://www.diw.de/documents/publikationen/73/diw_01.c.901039.de/dp2082.pdf</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>Cross-check only (not the quantitative source): shows literature H2-DRI investment-cost estimates vary widely and can be sticky, supporting a moderate (not maximal) capacity-doublings assumption for the learning-curve trajectory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>capex_trajectory</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>steel_ngdri_eaf</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>General one-factor learning-curve meta-analysis; mature-process-kit LR band (3-5%) applied to transitional NG-DRI+EAF's 2025-2050 capex trajectory (4% LR x ~1 assumed EU capacity doubling, ~4% total decline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>capex_trajectory</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>cement_clinkersub</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>General one-factor learning-curve meta-analysis; novel-process-equipment LR band (8-12%) applied to LC3 clinker substitution's 2025-2050 capex trajectory (8% LR x ~1.5 assumed EU capacity doublings, ~12% total decline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>capex_trajectory</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>hvc_bio</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>General one-factor learning-curve meta-analysis; mature-process-kit LR band (3-5%) applied to bio-naphtha cracking's 2025-2050 capex trajectory (4% LR x ~1 assumed EU capacity doubling, ~4% total decline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>capex_trajectory</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>multiple (CCS variants; paper_elec; paper_bio; ammonia_h2; hvc_elec; glass_elec; glass_hybrid; cement_altfuel)</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Technology Data catalogue series (Industrial Process Heat; Carbon Capture, Transport and Storage; Renewable Fuels)</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>2024-2026</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>2025/30/40/50 (2035/45 interpolated) DEA per-sheet cost projections re-used to derive the relative 2025-&gt;2050 CAPEX decline PROFILE applied to each tech's technologies.csv 2025 capex anchor (for CCS variants, the profile is applied only to the capture add-on portion; base process capex held flat). See capex_trajectory.csv basis column per tech/year for the exact sheet and computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>scenarios</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>learning_fast / learning_slow</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>ESABCC Method Hub (model team)</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Model README - sensitivity scenario methodology</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>beta/modules/summer-prep/optimization/model/README.md</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Two new sensitivity scenarios varying the capex-decline exponent (factor 1.5 / 0.5) applied to the capex_trajectory.csv ratio-to-2025 profile; prototype modelling assumptions, not independent literature values.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G80"/>
+  <autoFilter ref="A1:G88"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -4242,6 +5371,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7012,6 +8148,4413 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F151"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>capex_eur_t</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>steel_bfbof</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. BF-BOF is the fully mature global-incumbent steelmaking route; no further unit-capex learning expected.</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>steel_bfbof</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. BF-BOF is the fully mature global-incumbent steelmaking route; no further unit-capex learning expected.</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>steel_bfbof</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. BF-BOF is the fully mature global-incumbent steelmaking route; no further unit-capex learning expected.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>steel_bfbof</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. BF-BOF is the fully mature global-incumbent steelmaking route; no further unit-capex learning expected.</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>steel_bfbof</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. BF-BOF is the fully mature global-incumbent steelmaking route; no further unit-capex learning expected.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>steel_bfbof</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. BF-BOF is the fully mature global-incumbent steelmaking route; no further unit-capex learning expected.</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>cement_ref</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Conventional dry-kiln clinker production is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>cement_ref</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Conventional dry-kiln clinker production is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>cement_ref</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Conventional dry-kiln clinker production is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>cement_ref</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Conventional dry-kiln clinker production is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>cement_ref</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Conventional dry-kiln clinker production is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>cement_ref</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Conventional dry-kiln clinker production is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>IEA / CSI (2018), Technology Roadmap: Low-Carbon Transition in the Cement Industry</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/technology-roadmap-low-carbon-transition-in-the-cement-industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>hvc_ref</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. NG/naphtha steam cracking is a fully mature process with no expected further capex learning.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>hvc_ref</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. NG/naphtha steam cracking is a fully mature process with no expected further capex learning.</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>hvc_ref</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. NG/naphtha steam cracking is a fully mature process with no expected further capex learning.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>hvc_ref</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. NG/naphtha steam cracking is a fully mature process with no expected further capex learning.</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>hvc_ref</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. NG/naphtha steam cracking is a fully mature process with no expected further capex learning.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>hvc_ref</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. NG/naphtha steam cracking is a fully mature process with no expected further capex learning.</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2018), The Future of Petrochemicals</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/the-future-of-petrochemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_smr</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>650</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. SMR Haber-Bosch ammonia synthesis is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_smr</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>650</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. SMR Haber-Bosch ammonia synthesis is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_smr</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>650</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. SMR Haber-Bosch ammonia synthesis is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_smr</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>650</v>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. SMR Haber-Bosch ammonia synthesis is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_smr</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>650</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. SMR Haber-Bosch ammonia synthesis is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_smr</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>650</v>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. SMR Haber-Bosch ammonia synthesis is a fully mature, century-old process.</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2021), Ammonia Technology Roadmap</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/ammonia-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>alu_ref</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Hall-Heroult primary smelting is a fully mature process; carbon-anode cell capex has been stable for decades.</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>alu_ref</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Hall-Heroult primary smelting is a fully mature process; carbon-anode cell capex has been stable for decades.</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>alu_ref</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Hall-Heroult primary smelting is a fully mature process; carbon-anode cell capex has been stable for decades.</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>alu_ref</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Hall-Heroult primary smelting is a fully mature process; carbon-anode cell capex has been stable for decades.</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>alu_ref</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Hall-Heroult primary smelting is a fully mature process; carbon-anode cell capex has been stable for decades.</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>alu_ref</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Hall-Heroult primary smelting is a fully mature process; carbon-anode cell capex has been stable for decades.</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>JRC (European Commission) (2026), Aluminium factsheet (JRC144120)</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC144120/Aluminium_factsheet_JRC144120.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>alu_sec</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Secondary (scrap-based) aluminium remelting is a mature, low-capex process; scrap availability (not capex) is the binding constraint.</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>alu_sec</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Secondary (scrap-based) aluminium remelting is a mature, low-capex process; scrap availability (not capex) is the binding constraint.</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>alu_sec</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Secondary (scrap-based) aluminium remelting is a mature, low-capex process; scrap availability (not capex) is the binding constraint.</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>alu_sec</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Secondary (scrap-based) aluminium remelting is a mature, low-capex process; scrap availability (not capex) is the binding constraint.</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>alu_sec</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Secondary (scrap-based) aluminium remelting is a mature, low-capex process; scrap availability (not capex) is the binding constraint.</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>alu_sec</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Secondary (scrap-based) aluminium remelting is a mature, low-capex process; scrap availability (not capex) is the binding constraint.</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>glass_ng</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas fired glass melting is the mature reference furnace technology.</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>glass_ng</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas fired glass melting is the mature reference furnace technology.</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>glass_ng</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas fired glass melting is the mature reference furnace technology.</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>glass_ng</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas fired glass melting is the mature reference furnace technology.</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>glass_ng</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas fired glass melting is the mature reference furnace technology.</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>glass_ng</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas fired glass melting is the mature reference furnace technology.</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>European Commission (CINEA) (2022), How LIFE is reducing emissions from glass production</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/news-events/news/how-life-reducing-emissions-glass-production-2022-03-16_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>paper_ref</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas CHP process heat is the mature reference technology for pulp &amp; paper.</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>paper_ref</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C45" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas CHP process heat is the mature reference technology for pulp &amp; paper.</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>paper_ref</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas CHP process heat is the mature reference technology for pulp &amp; paper.</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>paper_ref</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C47" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas CHP process heat is the mature reference technology for pulp &amp; paper.</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>paper_ref</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas CHP process heat is the mature reference technology for pulp &amp; paper.</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>paper_ref</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C49" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Natural-gas CHP process heat is the mature reference technology for pulp &amp; paper.</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>CEPI (2022), Key Statistics 2022 - European pulp &amp; paper industry</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cepi.org/wp-content/uploads/2023/07/2022-Key-Statistics-FINAL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>steel_scrap_eaf</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Scrap-EAF is a mature process; scrap availability (not capex) is the binding long-run constraint.</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap; Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>steel_scrap_eaf</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Scrap-EAF is a mature process; scrap availability (not capex) is the binding long-run constraint.</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap; Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>steel_scrap_eaf</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Scrap-EAF is a mature process; scrap availability (not capex) is the binding long-run constraint.</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap; Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>steel_scrap_eaf</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Scrap-EAF is a mature process; scrap availability (not capex) is the binding long-run constraint.</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap; Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>steel_scrap_eaf</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Scrap-EAF is a mature process; scrap availability (not capex) is the binding long-run constraint.</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap; Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>steel_scrap_eaf</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Mature technology - no learning assumed; capex held flat at the 2025 reference level. Scrap-EAF is a mature process; scrap availability (not capex) is the binding long-run constraint.</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>IEA (2020), Iron and Steel Technology Roadmap; Material Economics (2019), Industrial Transformation 2050</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/iron-and-steel-technology-roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>steel_bfbof_ccs</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>770</v>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit, cement-kiln flue gas used as CO2-concentration proxy for BF-BOF flue/top gas, per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 770 total minus 400 EUR/(t/yr) base-process capex); base process (steel_bfbof, IEA (2020) Iron and Steel Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>steel_bfbof_ccs</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>708</v>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit, cement-kiln flue gas used as CO2-concentration proxy for BF-BOF flue/top gas, per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 770 total minus 400 EUR/(t/yr) base-process capex); base process (steel_bfbof, IEA (2020) Iron and Steel Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>steel_bfbof_ccs</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>684</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit, cement-kiln flue gas used as CO2-concentration proxy for BF-BOF flue/top gas, per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 770 total minus 400 EUR/(t/yr) base-process capex); base process (steel_bfbof, IEA (2020) Iron and Steel Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>steel_bfbof_ccs</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>659</v>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit, cement-kiln flue gas used as CO2-concentration proxy for BF-BOF flue/top gas, per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 770 total minus 400 EUR/(t/yr) base-process capex); base process (steel_bfbof, IEA (2020) Iron and Steel Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>steel_bfbof_ccs</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>653</v>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit, cement-kiln flue gas used as CO2-concentration proxy for BF-BOF flue/top gas, per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 770 total minus 400 EUR/(t/yr) base-process capex); base process (steel_bfbof, IEA (2020) Iron and Steel Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>steel_bfbof_ccs</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C61" s="19" t="n">
+        <v>647</v>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit, cement-kiln flue gas used as CO2-concentration proxy for BF-BOF flue/top gas, per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 770 total minus 400 EUR/(t/yr) base-process capex); base process (steel_bfbof, IEA (2020) Iron and Steel Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>cement_ccs</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>325</v>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit for a 4500 t clinker/day cement kiln - direct match) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 175 EUR/(t/yr) = 325 total minus 150 EUR/(t/yr) base-process capex); base process (cement_ref, IEA/CSI (2018) Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>cement_ccs</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>296</v>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit for a 4500 t clinker/day cement kiln - direct match) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 175 EUR/(t/yr) = 325 total minus 150 EUR/(t/yr) base-process capex); base process (cement_ref, IEA/CSI (2018) Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>cement_ccs</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>284</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit for a 4500 t clinker/day cement kiln - direct match) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 175 EUR/(t/yr) = 325 total minus 150 EUR/(t/yr) base-process capex); base process (cement_ref, IEA/CSI (2018) Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>cement_ccs</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>272</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit for a 4500 t clinker/day cement kiln - direct match) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 175 EUR/(t/yr) = 325 total minus 150 EUR/(t/yr) base-process capex); base process (cement_ref, IEA/CSI (2018) Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>cement_ccs</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>270</v>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit for a 4500 t clinker/day cement kiln - direct match) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 175 EUR/(t/yr) = 325 total minus 150 EUR/(t/yr) base-process capex); base process (cement_ref, IEA/CSI (2018) Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>cement_ccs</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C67" s="19" t="n">
+        <v>267</v>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture retrofit for a 4500 t clinker/day cement kiln - direct match) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 175 EUR/(t/yr) = 325 total minus 150 EUR/(t/yr) base-process capex); base process (cement_ref, IEA/CSI (2018) Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_smr_ccs</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture on cement-kiln-like moderate-concentration flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 1020 total minus 650 EUR/(t/yr) base-process capex); base process (ammonia_smr, IEA (2021) Ammonia Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_smr_ccs</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C69" s="19" t="n">
+        <v>958</v>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture on cement-kiln-like moderate-concentration flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 1020 total minus 650 EUR/(t/yr) base-process capex); base process (ammonia_smr, IEA (2021) Ammonia Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_smr_ccs</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>934</v>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture on cement-kiln-like moderate-concentration flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 1020 total minus 650 EUR/(t/yr) base-process capex); base process (ammonia_smr, IEA (2021) Ammonia Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_smr_ccs</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C71" s="19" t="n">
+        <v>909</v>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture on cement-kiln-like moderate-concentration flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 1020 total minus 650 EUR/(t/yr) base-process capex); base process (ammonia_smr, IEA (2021) Ammonia Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_smr_ccs</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>903</v>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture on cement-kiln-like moderate-concentration flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 1020 total minus 650 EUR/(t/yr) base-process capex); base process (ammonia_smr, IEA (2021) Ammonia Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_smr_ccs</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C73" s="19" t="n">
+        <v>897</v>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.c (post-combustion capture on cement-kiln-like moderate-concentration flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 370 EUR/(t/yr) = 1020 total minus 650 EUR/(t/yr) base-process capex); base process (ammonia_smr, IEA (2021) Ammonia Technology Roadmap) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>hvc_ccs</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.a (post-combustion capture retrofit on a dilute ~15% CO2 CHP/biomass flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 320 EUR/(t/yr) = 1020 total minus 700 EUR/(t/yr) base-process capex); base process (hvc_ref, IEA (2018) The Future of Petrochemicals) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>hvc_ccs</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C75" s="19" t="n">
+        <v>960</v>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.a (post-combustion capture retrofit on a dilute ~15% CO2 CHP/biomass flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 320 EUR/(t/yr) = 1020 total minus 700 EUR/(t/yr) base-process capex); base process (hvc_ref, IEA (2018) The Future of Petrochemicals) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>hvc_ccs</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C76" s="16" t="n">
+        <v>941</v>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.a (post-combustion capture retrofit on a dilute ~15% CO2 CHP/biomass flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 320 EUR/(t/yr) = 1020 total minus 700 EUR/(t/yr) base-process capex); base process (hvc_ref, IEA (2018) The Future of Petrochemicals) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>hvc_ccs</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C77" s="19" t="n">
+        <v>922</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.a (post-combustion capture retrofit on a dilute ~15% CO2 CHP/biomass flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 320 EUR/(t/yr) = 1020 total minus 700 EUR/(t/yr) base-process capex); base process (hvc_ref, IEA (2018) The Future of Petrochemicals) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>hvc_ccs</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C78" s="16" t="n">
+        <v>914</v>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.a (post-combustion capture retrofit on a dilute ~15% CO2 CHP/biomass flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 320 EUR/(t/yr) = 1020 total minus 700 EUR/(t/yr) base-process capex); base process (hvc_ref, IEA (2018) The Future of Petrochemicals) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>hvc_ccs</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C79" s="19" t="n">
+        <v>906</v>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>DEA CCTS sheet 401.a (post-combustion capture retrofit on a dilute ~15% CO2 CHP/biomass flue gas, closest available DEA proxy per technologies.csv) specific-investment cost projection (2025/30/40/50 published; 2035/45 linearly interpolated) applied as a relative decline profile to the capture add-on portion of 2025 capex (add-on = 320 EUR/(t/yr) = 1020 total minus 700 EUR/(t/yr) base-process capex); base process (hvc_ref, IEA (2018) The Future of Petrochemicals) held flat since it is a mature, separately-sourced reference technology.</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2024), Technology Data for Carbon Capture, Transport and Storage</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>paper_elec</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C80" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 2.a (high-temperature heat pump up to 125degC) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 300 EUR/(t/yr) 2025 anchor. Nominal investment declines 1.20-&gt;1.15-&gt;1.10-&gt;1.05-&gt;1.00 MEUR/MW over 2025-2050 (DEA-published 5-yr steps, no interpolation needed).</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>paper_elec</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C81" s="19" t="n">
+        <v>288</v>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 2.a (high-temperature heat pump up to 125degC) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 300 EUR/(t/yr) 2025 anchor. Nominal investment declines 1.20-&gt;1.15-&gt;1.10-&gt;1.05-&gt;1.00 MEUR/MW over 2025-2050 (DEA-published 5-yr steps, no interpolation needed).</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>paper_elec</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C82" s="16" t="n">
+        <v>275</v>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 2.a (high-temperature heat pump up to 125degC) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 300 EUR/(t/yr) 2025 anchor. Nominal investment declines 1.20-&gt;1.15-&gt;1.10-&gt;1.05-&gt;1.00 MEUR/MW over 2025-2050 (DEA-published 5-yr steps, no interpolation needed).</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>paper_elec</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C83" s="19" t="n">
+        <v>263</v>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 2.a (high-temperature heat pump up to 125degC) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 300 EUR/(t/yr) 2025 anchor. Nominal investment declines 1.20-&gt;1.15-&gt;1.10-&gt;1.05-&gt;1.00 MEUR/MW over 2025-2050 (DEA-published 5-yr steps, no interpolation needed).</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>paper_elec</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C84" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 2.a (high-temperature heat pump up to 125degC) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 300 EUR/(t/yr) 2025 anchor. Nominal investment declines 1.20-&gt;1.15-&gt;1.10-&gt;1.05-&gt;1.00 MEUR/MW over 2025-2050 (DEA-published 5-yr steps, no interpolation needed).</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>paper_elec</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C85" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 2.a (high-temperature heat pump up to 125degC) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 300 EUR/(t/yr) 2025 anchor. Nominal investment declines 1.20-&gt;1.15-&gt;1.10-&gt;1.05-&gt;1.00 MEUR/MW over 2025-2050 (DEA-published 5-yr steps, no interpolation needed).</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>paper_bio</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 6.2 (biomass boiler) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 230 EUR/(t/yr) 2025 anchor. Nominal investment declines 0.878-&gt;0.829-&gt;0.807-&gt;0.786-&gt;0.742 MEUR/MW over 2025-2050 (DEA-published 5-yr steps).</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>paper_bio</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C87" s="19" t="n">
+        <v>217</v>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 6.2 (biomass boiler) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 230 EUR/(t/yr) 2025 anchor. Nominal investment declines 0.878-&gt;0.829-&gt;0.807-&gt;0.786-&gt;0.742 MEUR/MW over 2025-2050 (DEA-published 5-yr steps).</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>paper_bio</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C88" s="16" t="n">
+        <v>211</v>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 6.2 (biomass boiler) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 230 EUR/(t/yr) 2025 anchor. Nominal investment declines 0.878-&gt;0.829-&gt;0.807-&gt;0.786-&gt;0.742 MEUR/MW over 2025-2050 (DEA-published 5-yr steps).</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>paper_bio</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C89" s="19" t="n">
+        <v>206</v>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 6.2 (biomass boiler) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 230 EUR/(t/yr) 2025 anchor. Nominal investment declines 0.878-&gt;0.829-&gt;0.807-&gt;0.786-&gt;0.742 MEUR/MW over 2025-2050 (DEA-published 5-yr steps).</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>paper_bio</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C90" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 6.2 (biomass boiler) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 230 EUR/(t/yr) 2025 anchor. Nominal investment declines 0.878-&gt;0.829-&gt;0.807-&gt;0.786-&gt;0.742 MEUR/MW over 2025-2050 (DEA-published 5-yr steps).</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>paper_bio</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C91" s="19" t="n">
+        <v>194</v>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 6.2 (biomass boiler) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 230 EUR/(t/yr) 2025 anchor. Nominal investment declines 0.878-&gt;0.829-&gt;0.807-&gt;0.786-&gt;0.742 MEUR/MW over 2025-2050 (DEA-published 5-yr steps).</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_h2</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C92" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>DEA Renewable Fuels sheet 5.4 (Hydrogen to Ammonia, Haber-Bosch synthesis) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 1000 EUR/(t/yr) 2025 anchor. Specific investment declines from DEA-published 2020/2030/2040/2050 points (1.687-&gt;1.380-&gt;1.128-&gt;0.865 MEUR/MW NH3); 2025 and 2035 linearly interpolated (as per technologies.csv 2025/26 anchor derivation).</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_h2</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C93" s="19" t="n">
+        <v>900</v>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>DEA Renewable Fuels sheet 5.4 (Hydrogen to Ammonia, Haber-Bosch synthesis) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 1000 EUR/(t/yr) 2025 anchor. Specific investment declines from DEA-published 2020/2030/2040/2050 points (1.687-&gt;1.380-&gt;1.128-&gt;0.865 MEUR/MW NH3); 2025 and 2035 linearly interpolated (as per technologies.csv 2025/26 anchor derivation).</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_h2</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C94" s="16" t="n">
+        <v>818</v>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>DEA Renewable Fuels sheet 5.4 (Hydrogen to Ammonia, Haber-Bosch synthesis) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 1000 EUR/(t/yr) 2025 anchor. Specific investment declines from DEA-published 2020/2030/2040/2050 points (1.687-&gt;1.380-&gt;1.128-&gt;0.865 MEUR/MW NH3); 2025 and 2035 linearly interpolated (as per technologies.csv 2025/26 anchor derivation).</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_h2</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C95" s="19" t="n">
+        <v>736</v>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>DEA Renewable Fuels sheet 5.4 (Hydrogen to Ammonia, Haber-Bosch synthesis) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 1000 EUR/(t/yr) 2025 anchor. Specific investment declines from DEA-published 2020/2030/2040/2050 points (1.687-&gt;1.380-&gt;1.128-&gt;0.865 MEUR/MW NH3); 2025 and 2035 linearly interpolated (as per technologies.csv 2025/26 anchor derivation).</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>ammonia_h2</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C96" s="16" t="n">
+        <v>650</v>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>DEA Renewable Fuels sheet 5.4 (Hydrogen to Ammonia, Haber-Bosch synthesis) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 1000 EUR/(t/yr) 2025 anchor. Specific investment declines from DEA-published 2020/2030/2040/2050 points (1.687-&gt;1.380-&gt;1.128-&gt;0.865 MEUR/MW NH3); 2025 and 2035 linearly interpolated (as per technologies.csv 2025/26 anchor derivation).</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>ammonia_h2</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C97" s="19" t="n">
+        <v>564</v>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>DEA Renewable Fuels sheet 5.4 (Hydrogen to Ammonia, Haber-Bosch synthesis) nominal/specific investment cost projection (2025-2050) applied directly as a relative decline profile to the 1000 EUR/(t/yr) 2025 anchor. Specific investment declines from DEA-published 2020/2030/2040/2050 points (1.687-&gt;1.380-&gt;1.128-&gt;0.865 MEUR/MW NH3); 2025 and 2035 linearly interpolated (as per technologies.csv 2025/26 anchor derivation).</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Renewable Fuels</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>hvc_elec</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C98" s="16" t="n">
+        <v>850</v>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 850 EUR/(t/yr) anchor. Real-world e-cracker cost trends are governed by cracker tubes/compressors/separation train (BASF-anchored capex, per technologies.csv), not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>hvc_elec</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C99" s="19" t="n">
+        <v>850</v>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 850 EUR/(t/yr) anchor. Real-world e-cracker cost trends are governed by cracker tubes/compressors/separation train (BASF-anchored capex, per technologies.csv), not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>hvc_elec</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C100" s="16" t="n">
+        <v>850</v>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 850 EUR/(t/yr) anchor. Real-world e-cracker cost trends are governed by cracker tubes/compressors/separation train (BASF-anchored capex, per technologies.csv), not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>hvc_elec</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C101" s="19" t="n">
+        <v>850</v>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 850 EUR/(t/yr) anchor. Real-world e-cracker cost trends are governed by cracker tubes/compressors/separation train (BASF-anchored capex, per technologies.csv), not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>hvc_elec</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C102" s="16" t="n">
+        <v>850</v>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 850 EUR/(t/yr) anchor. Real-world e-cracker cost trends are governed by cracker tubes/compressors/separation train (BASF-anchored capex, per technologies.csv), not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>hvc_elec</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C103" s="19" t="n">
+        <v>850</v>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 850 EUR/(t/yr) anchor. Real-world e-cracker cost trends are governed by cracker tubes/compressors/separation train (BASF-anchored capex, per technologies.csv), not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>glass_elec</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C104" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 150 EUR/(t/yr) anchor. Real furnace-rebuild capex (IEA ETP-anchored, per technologies.csv) is dominated by shell/refractories/forming equipment, not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>glass_elec</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C105" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 150 EUR/(t/yr) anchor. Real furnace-rebuild capex (IEA ETP-anchored, per technologies.csv) is dominated by shell/refractories/forming equipment, not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>glass_elec</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C106" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 150 EUR/(t/yr) anchor. Real furnace-rebuild capex (IEA ETP-anchored, per technologies.csv) is dominated by shell/refractories/forming equipment, not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>glass_elec</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C107" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 150 EUR/(t/yr) anchor. Real furnace-rebuild capex (IEA ETP-anchored, per technologies.csv) is dominated by shell/refractories/forming equipment, not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>glass_elec</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C108" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 150 EUR/(t/yr) anchor. Real furnace-rebuild capex (IEA ETP-anchored, per technologies.csv) is dominated by shell/refractories/forming equipment, not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>glass_elec</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C109" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.3 (direct electric firing) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 150 EUR/(t/yr) anchor. Real furnace-rebuild capex (IEA ETP-anchored, per technologies.csv) is dominated by shell/refractories/forming equipment, not priced by this heating-element-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>cement_altfuel</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C110" s="16" t="n">
+        <v>165</v>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.2 (direct firing, solid fuels) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 165 EUR/(t/yr) anchor. Kiln shell/refractories/preheater (IEA/CSI-anchored, per technologies.csv) dominate cement-kiln capex, not priced by this burner-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>cement_altfuel</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C111" s="19" t="n">
+        <v>165</v>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.2 (direct firing, solid fuels) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 165 EUR/(t/yr) anchor. Kiln shell/refractories/preheater (IEA/CSI-anchored, per technologies.csv) dominate cement-kiln capex, not priced by this burner-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>cement_altfuel</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C112" s="16" t="n">
+        <v>165</v>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.2 (direct firing, solid fuels) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 165 EUR/(t/yr) anchor. Kiln shell/refractories/preheater (IEA/CSI-anchored, per technologies.csv) dominate cement-kiln capex, not priced by this burner-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>cement_altfuel</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C113" s="19" t="n">
+        <v>165</v>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.2 (direct firing, solid fuels) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 165 EUR/(t/yr) anchor. Kiln shell/refractories/preheater (IEA/CSI-anchored, per technologies.csv) dominate cement-kiln capex, not priced by this burner-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>cement_altfuel</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C114" s="16" t="n">
+        <v>165</v>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.2 (direct firing, solid fuels) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 165 EUR/(t/yr) anchor. Kiln shell/refractories/preheater (IEA/CSI-anchored, per technologies.csv) dominate cement-kiln capex, not priced by this burner-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>cement_altfuel</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C115" s="19" t="n">
+        <v>165</v>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheet 7.2 (direct firing, solid fuels) shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 165 EUR/(t/yr) anchor. Kiln shell/refractories/preheater (IEA/CSI-anchored, per technologies.csv) dominate cement-kiln capex, not priced by this burner-only DEA sheet.</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>glass_hybrid</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C116" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheets 7.3 (electric) &amp; 6.1 (gas/oil boiler) blend shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 140 EUR/(t/yr) anchor. Both underlying DEA proxy sheets show flat nominal investment 2025-2050; full hybrid-furnace capex (IEA ETP-anchored, per technologies.csv) held flat accordingly.</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>glass_hybrid</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C117" s="19" t="n">
+        <v>140</v>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheets 7.3 (electric) &amp; 6.1 (gas/oil boiler) blend shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 140 EUR/(t/yr) anchor. Both underlying DEA proxy sheets show flat nominal investment 2025-2050; full hybrid-furnace capex (IEA ETP-anchored, per technologies.csv) held flat accordingly.</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>glass_hybrid</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C118" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheets 7.3 (electric) &amp; 6.1 (gas/oil boiler) blend shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 140 EUR/(t/yr) anchor. Both underlying DEA proxy sheets show flat nominal investment 2025-2050; full hybrid-furnace capex (IEA ETP-anchored, per technologies.csv) held flat accordingly.</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>glass_hybrid</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C119" s="19" t="n">
+        <v>140</v>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheets 7.3 (electric) &amp; 6.1 (gas/oil boiler) blend shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 140 EUR/(t/yr) anchor. Both underlying DEA proxy sheets show flat nominal investment 2025-2050; full hybrid-furnace capex (IEA ETP-anchored, per technologies.csv) held flat accordingly.</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>glass_hybrid</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C120" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheets 7.3 (electric) &amp; 6.1 (gas/oil boiler) blend shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 140 EUR/(t/yr) anchor. Both underlying DEA proxy sheets show flat nominal investment 2025-2050; full hybrid-furnace capex (IEA ETP-anchored, per technologies.csv) held flat accordingly.</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>glass_hybrid</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C121" s="19" t="n">
+        <v>140</v>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>DEA Industrial Process Heat sheets 7.3 (electric) &amp; 6.1 (gas/oil boiler) blend shows a FLAT nominal/specific investment (no decline 2025-2050) for this proxy sheet - equipment is simple/mature (heating elements, burners); applied as a flat trajectory to the 140 EUR/(t/yr) anchor. Both underlying DEA proxy sheets show flat nominal investment 2025-2050; full hybrid-furnace capex (IEA ETP-anchored, per technologies.csv) held flat accordingly.</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>Danish Energy Agency (2026), Technology Data for Industrial Process Heat</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="inlineStr">
+        <is>
+          <t>https://ens.dk/en/analyses-and-statistics/technology-data-industrial-process-heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>steel_h2dri_eaf</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C122" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>LR 18%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 32.8% capex decline by 2050 (~1.58%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (IRENA reports 16-21% for electrolysers/fuel cells); ~2 doublings reflects EU H2-DRI scaling from a handful of plants today (LeadIT Green Steel Tracker) to a material EU steel share by 2050. DIW (2024) Revisiting Investment Costs for Green Steel is a cross-check that literature H2-DRI capex estimates vary widely and can be sticky, so a moderate (not maximal) doublings count was chosen.</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>steel_h2dri_eaf</t>
+        </is>
+      </c>
+      <c r="B123" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C123" s="19" t="n">
+        <v>739</v>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>LR 18%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 32.8% capex decline by 2050 (~1.58%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (IRENA reports 16-21% for electrolysers/fuel cells); ~2 doublings reflects EU H2-DRI scaling from a handful of plants today (LeadIT Green Steel Tracker) to a material EU steel share by 2050. DIW (2024) Revisiting Investment Costs for Green Steel is a cross-check that literature H2-DRI capex estimates vary widely and can be sticky, so a moderate (not maximal) doublings count was chosen.</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>steel_h2dri_eaf</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C124" s="16" t="n">
+        <v>683</v>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>LR 18%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 32.8% capex decline by 2050 (~1.58%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (IRENA reports 16-21% for electrolysers/fuel cells); ~2 doublings reflects EU H2-DRI scaling from a handful of plants today (LeadIT Green Steel Tracker) to a material EU steel share by 2050. DIW (2024) Revisiting Investment Costs for Green Steel is a cross-check that literature H2-DRI capex estimates vary widely and can be sticky, so a moderate (not maximal) doublings count was chosen.</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>steel_h2dri_eaf</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C125" s="19" t="n">
+        <v>630</v>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>LR 18%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 32.8% capex decline by 2050 (~1.58%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (IRENA reports 16-21% for electrolysers/fuel cells); ~2 doublings reflects EU H2-DRI scaling from a handful of plants today (LeadIT Green Steel Tracker) to a material EU steel share by 2050. DIW (2024) Revisiting Investment Costs for Green Steel is a cross-check that literature H2-DRI capex estimates vary widely and can be sticky, so a moderate (not maximal) doublings count was chosen.</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>steel_h2dri_eaf</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C126" s="16" t="n">
+        <v>582</v>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>LR 18%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 32.8% capex decline by 2050 (~1.58%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (IRENA reports 16-21% for electrolysers/fuel cells); ~2 doublings reflects EU H2-DRI scaling from a handful of plants today (LeadIT Green Steel Tracker) to a material EU steel share by 2050. DIW (2024) Revisiting Investment Costs for Green Steel is a cross-check that literature H2-DRI capex estimates vary widely and can be sticky, so a moderate (not maximal) doublings count was chosen.</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>steel_h2dri_eaf</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C127" s="19" t="n">
+        <v>538</v>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>LR 18%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 32.8% capex decline by 2050 (~1.58%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (IRENA reports 16-21% for electrolysers/fuel cells); ~2 doublings reflects EU H2-DRI scaling from a handful of plants today (LeadIT Green Steel Tracker) to a material EU steel share by 2050. DIW (2024) Revisiting Investment Costs for Green Steel is a cross-check that literature H2-DRI capex estimates vary widely and can be sticky, so a moderate (not maximal) doublings count was chosen.</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>steel_ngdri_eaf</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C128" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature process kit LR band (3-5%, per Rubin et al. general one-factor learning-curve meta-analysis); NG-DRI+EAF is a transitional but already-commercial route (deployed at scale outside the EU), so only modest further EU scale-up/learning is assumed before it is superseded by H2-DRI.</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>steel_ngdri_eaf</t>
+        </is>
+      </c>
+      <c r="B129" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C129" s="19" t="n">
+        <v>496</v>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature process kit LR band (3-5%, per Rubin et al. general one-factor learning-curve meta-analysis); NG-DRI+EAF is a transitional but already-commercial route (deployed at scale outside the EU), so only modest further EU scale-up/learning is assumed before it is superseded by H2-DRI.</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>steel_ngdri_eaf</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C130" s="16" t="n">
+        <v>492</v>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature process kit LR band (3-5%, per Rubin et al. general one-factor learning-curve meta-analysis); NG-DRI+EAF is a transitional but already-commercial route (deployed at scale outside the EU), so only modest further EU scale-up/learning is assumed before it is superseded by H2-DRI.</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>steel_ngdri_eaf</t>
+        </is>
+      </c>
+      <c r="B131" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C131" s="19" t="n">
+        <v>488</v>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature process kit LR band (3-5%, per Rubin et al. general one-factor learning-curve meta-analysis); NG-DRI+EAF is a transitional but already-commercial route (deployed at scale outside the EU), so only modest further EU scale-up/learning is assumed before it is superseded by H2-DRI.</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>steel_ngdri_eaf</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C132" s="16" t="n">
+        <v>484</v>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature process kit LR band (3-5%, per Rubin et al. general one-factor learning-curve meta-analysis); NG-DRI+EAF is a transitional but already-commercial route (deployed at scale outside the EU), so only modest further EU scale-up/learning is assumed before it is superseded by H2-DRI.</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>steel_ngdri_eaf</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C133" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature process kit LR band (3-5%, per Rubin et al. general one-factor learning-curve meta-analysis); NG-DRI+EAF is a transitional but already-commercial route (deployed at scale outside the EU), so only modest further EU scale-up/learning is assumed before it is superseded by H2-DRI.</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>alu_inert</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C134" s="16" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>LR 15%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 27.8% capex decline by 2050 (~1.29%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (lower end of IRENA's 16-21% electrolyser/fuel-cell range, since inert-anode cells are a cell-technology retrofit rather than a modular stack); ELYSIS (2025) achieved its first commercial-size cell in Nov 2025, so ~2 doublings by 2050 is assumed as deployment scales from first-of-a-kind to a wider EU rollout.</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>alu_inert</t>
+        </is>
+      </c>
+      <c r="B135" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C135" s="19" t="n">
+        <v>3561</v>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>LR 15%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 27.8% capex decline by 2050 (~1.29%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (lower end of IRENA's 16-21% electrolyser/fuel-cell range, since inert-anode cells are a cell-technology retrofit rather than a modular stack); ELYSIS (2025) achieved its first commercial-size cell in Nov 2025, so ~2 doublings by 2050 is assumed as deployment scales from first-of-a-kind to a wider EU rollout.</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>alu_inert</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C136" s="16" t="n">
+        <v>3337</v>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>LR 15%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 27.8% capex decline by 2050 (~1.29%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (lower end of IRENA's 16-21% electrolyser/fuel-cell range, since inert-anode cells are a cell-technology retrofit rather than a modular stack); ELYSIS (2025) achieved its first commercial-size cell in Nov 2025, so ~2 doublings by 2050 is assumed as deployment scales from first-of-a-kind to a wider EU rollout.</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>alu_inert</t>
+        </is>
+      </c>
+      <c r="B137" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C137" s="19" t="n">
+        <v>3127</v>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>LR 15%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 27.8% capex decline by 2050 (~1.29%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (lower end of IRENA's 16-21% electrolyser/fuel-cell range, since inert-anode cells are a cell-technology retrofit rather than a modular stack); ELYSIS (2025) achieved its first commercial-size cell in Nov 2025, so ~2 doublings by 2050 is assumed as deployment scales from first-of-a-kind to a wider EU rollout.</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>alu_inert</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C138" s="16" t="n">
+        <v>2930</v>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>LR 15%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 27.8% capex decline by 2050 (~1.29%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (lower end of IRENA's 16-21% electrolyser/fuel-cell range, since inert-anode cells are a cell-technology retrofit rather than a modular stack); ELYSIS (2025) achieved its first commercial-size cell in Nov 2025, so ~2 doublings by 2050 is assumed as deployment scales from first-of-a-kind to a wider EU rollout.</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>alu_inert</t>
+        </is>
+      </c>
+      <c r="B139" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C139" s="19" t="n">
+        <v>2745</v>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>LR 15%/doubling (one-factor learning rate) x ~2 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 27.8% capex decline by 2050 (~1.29%/yr, exponential decay applied at 5-yr steps). Electrolysis-adjacent LR band (lower end of IRENA's 16-21% electrolyser/fuel-cell range, since inert-anode cells are a cell-technology retrofit rather than a modular stack); ELYSIS (2025) achieved its first commercial-size cell in Nov 2025, so ~2 doublings by 2050 is assumed as deployment scales from first-of-a-kind to a wider EU rollout.</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>IRENA (2020), Green Hydrogen Cost Reduction: Scaling up Electrolysers to Meet the 1.5C Climate Goal</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2020/Dec/IRENA_Green_hydrogen_cost_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>cement_clinkersub</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C140" s="16" t="n">
+        <v>160</v>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>LR 8%/doubling (one-factor learning rate) x ~1.5 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 11.8% capex decline by 2050 (~0.50%/yr, exponential decay applied at 5-yr steps). Novel-process-equipment LR band (8-12%, per Rubin et al. general one-factor learning-curve meta-analysis); MDPI (2026) LC3 review reports the technology as already 'near-cost-neutral' and close to commercial readiness, consistent with only modest further learning (~1.5 doublings) as calcined-clay supply scales up.</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>cement_clinkersub</t>
+        </is>
+      </c>
+      <c r="B141" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C141" s="19" t="n">
+        <v>156</v>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>LR 8%/doubling (one-factor learning rate) x ~1.5 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 11.8% capex decline by 2050 (~0.50%/yr, exponential decay applied at 5-yr steps). Novel-process-equipment LR band (8-12%, per Rubin et al. general one-factor learning-curve meta-analysis); MDPI (2026) LC3 review reports the technology as already 'near-cost-neutral' and close to commercial readiness, consistent with only modest further learning (~1.5 doublings) as calcined-clay supply scales up.</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>cement_clinkersub</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C142" s="16" t="n">
+        <v>152</v>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>LR 8%/doubling (one-factor learning rate) x ~1.5 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 11.8% capex decline by 2050 (~0.50%/yr, exponential decay applied at 5-yr steps). Novel-process-equipment LR band (8-12%, per Rubin et al. general one-factor learning-curve meta-analysis); MDPI (2026) LC3 review reports the technology as already 'near-cost-neutral' and close to commercial readiness, consistent with only modest further learning (~1.5 doublings) as calcined-clay supply scales up.</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>cement_clinkersub</t>
+        </is>
+      </c>
+      <c r="B143" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C143" s="19" t="n">
+        <v>148</v>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>LR 8%/doubling (one-factor learning rate) x ~1.5 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 11.8% capex decline by 2050 (~0.50%/yr, exponential decay applied at 5-yr steps). Novel-process-equipment LR band (8-12%, per Rubin et al. general one-factor learning-curve meta-analysis); MDPI (2026) LC3 review reports the technology as already 'near-cost-neutral' and close to commercial readiness, consistent with only modest further learning (~1.5 doublings) as calcined-clay supply scales up.</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>cement_clinkersub</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C144" s="16" t="n">
+        <v>145</v>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>LR 8%/doubling (one-factor learning rate) x ~1.5 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 11.8% capex decline by 2050 (~0.50%/yr, exponential decay applied at 5-yr steps). Novel-process-equipment LR band (8-12%, per Rubin et al. general one-factor learning-curve meta-analysis); MDPI (2026) LC3 review reports the technology as already 'near-cost-neutral' and close to commercial readiness, consistent with only modest further learning (~1.5 doublings) as calcined-clay supply scales up.</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>cement_clinkersub</t>
+        </is>
+      </c>
+      <c r="B145" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C145" s="19" t="n">
+        <v>141</v>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>LR 8%/doubling (one-factor learning rate) x ~1.5 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 11.8% capex decline by 2050 (~0.50%/yr, exponential decay applied at 5-yr steps). Novel-process-equipment LR band (8-12%, per Rubin et al. general one-factor learning-curve meta-analysis); MDPI (2026) LC3 review reports the technology as already 'near-cost-neutral' and close to commercial readiness, consistent with only modest further learning (~1.5 doublings) as calcined-clay supply scales up.</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F145" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>hvc_bio</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C146" s="16" t="n">
+        <v>720</v>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature-process-kit LR band (3-5%, per Rubin et al.); bio-naphtha cracking reuses conventional cracker equipment (technologies.csv, IEA 2018) with only the feedstock switched, so minimal equipment-capex learning is expected beyond modest scale-up of bio-feedstock handling/pretreatment.</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>hvc_bio</t>
+        </is>
+      </c>
+      <c r="B147" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C147" s="19" t="n">
+        <v>714</v>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature-process-kit LR band (3-5%, per Rubin et al.); bio-naphtha cracking reuses conventional cracker equipment (technologies.csv, IEA 2018) with only the feedstock switched, so minimal equipment-capex learning is expected beyond modest scale-up of bio-feedstock handling/pretreatment.</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>hvc_bio</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C148" s="16" t="n">
+        <v>708</v>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature-process-kit LR band (3-5%, per Rubin et al.); bio-naphtha cracking reuses conventional cracker equipment (technologies.csv, IEA 2018) with only the feedstock switched, so minimal equipment-capex learning is expected beyond modest scale-up of bio-feedstock handling/pretreatment.</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>hvc_bio</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C149" s="19" t="n">
+        <v>703</v>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature-process-kit LR band (3-5%, per Rubin et al.); bio-naphtha cracking reuses conventional cracker equipment (technologies.csv, IEA 2018) with only the feedstock switched, so minimal equipment-capex learning is expected beyond modest scale-up of bio-feedstock handling/pretreatment.</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F149" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>hvc_bio</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C150" s="16" t="n">
+        <v>697</v>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature-process-kit LR band (3-5%, per Rubin et al.); bio-naphtha cracking reuses conventional cracker equipment (technologies.csv, IEA 2018) with only the feedstock switched, so minimal equipment-capex learning is expected beyond modest scale-up of bio-feedstock handling/pretreatment.</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>hvc_bio</t>
+        </is>
+      </c>
+      <c r="B151" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C151" s="19" t="n">
+        <v>691</v>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>LR 4%/doubling (one-factor learning rate) x ~1 cumulative EU capacity doublings assumed 2025-&gt;2050 =&gt; 4.0% capex decline by 2050 (~0.16%/yr, exponential decay applied at 5-yr steps). Mature-process-kit LR band (3-5%, per Rubin et al.); bio-naphtha cracking reuses conventional cracker equipment (technologies.csv, IEA 2018) with only the feedstock switched, so minimal equipment-capex learning is expected beyond modest scale-up of bio-feedstock handling/pretreatment.</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>Rubin, Azevedo, Jaramillo &amp; Yeh (2015), A Review of Learning Rates for Electricity Supply Technologies</t>
+        </is>
+      </c>
+      <c r="F151" s="13" t="inlineStr">
+        <is>
+          <t>https://www.cmu.edu/epp/iecm/rubin/PDF%20files/2015/A%20review%20of%20learning%20rates%20for%20electricity%20supply%20technologies.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F151"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId150"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8773,7 +14316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9832,7 +15375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10039,7 +15582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10400,757 +15943,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>subsector</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>steel</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D2" s="22" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>steel</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>2030</v>
-      </c>
-      <c r="D3" s="23" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>steel</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D4" s="22" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>steel</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="D5" s="23" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>steel</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>2045</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>steel</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>2050</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>aluminium</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>aluminium</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>2030</v>
-      </c>
-      <c r="D9" s="23" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>aluminium</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>aluminium</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="D11" s="23" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>aluminium</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>2045</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>scrap_share_max</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>aluminium</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>2050</v>
-      </c>
-      <c r="D13" s="23" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Material Economics (2019), Industrial Transformation 2050 - Pathways to Net-Zero Emissions from EU Heavy Industry</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>https://materialeconomics.com/sites/default/files/2024-06/material-economics-industrial-transformation-2050-executive-summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>biomass_pj_max</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>300</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>biomass_pj_max</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>2030</v>
-      </c>
-      <c r="D15" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>biomass_pj_max</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>300</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>biomass_pj_max</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="D17" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>biomass_pj_max</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>2045</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>300</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>biomass_pj_max</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>2050</v>
-      </c>
-      <c r="D19" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>JRC (European Commission) (2019), Brief on biomass for energy in the European Union</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/handle/JRC109354</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>ccs_mt_max</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>https://www.globalccsinstitute.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>ccs_mt_max</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="n">
-        <v>2030</v>
-      </c>
-      <c r="D21" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>https://www.globalccsinstitute.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>ccs_mt_max</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D22" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>https://www.globalccsinstitute.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>ccs_mt_max</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="D23" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>https://www.globalccsinstitute.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>ccs_mt_max</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>2045</v>
-      </c>
-      <c r="D24" s="22" t="n">
-        <v>80</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>https://www.globalccsinstitute.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>ccs_mt_max</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="n">
-        <v>2050</v>
-      </c>
-      <c r="D25" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Global CCS Institute (2024), Global Status of CCS report series; Clean Air Task Force (2025), Carbon capture and storage in Europe: slow but significant progress in 2025</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>https://www.globalccsinstitute.com/</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F25"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>